--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134851705</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134851657</v>
       </c>
       <c r="B3" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136487855</v>
       </c>
       <c r="B51" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136488085</v>
       </c>
       <c r="B52" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488093</v>
       </c>
       <c r="B53" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488195</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488215</v>
       </c>
       <c r="B55" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488233</v>
       </c>
       <c r="B56" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>136488052</v>
       </c>
       <c r="B188" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>136487945</v>
       </c>
       <c r="B189" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134851705</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134851657</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136487855</v>
       </c>
       <c r="B51" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136488085</v>
       </c>
       <c r="B52" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488093</v>
       </c>
       <c r="B53" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488195</v>
       </c>
       <c r="B54" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488215</v>
       </c>
       <c r="B55" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488233</v>
       </c>
       <c r="B56" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>136487945</v>
       </c>
       <c r="B189" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134851705</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134851657</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>134851586</v>
       </c>
       <c r="B32" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136487855</v>
       </c>
       <c r="B51" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136488085</v>
       </c>
       <c r="B52" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488093</v>
       </c>
       <c r="B53" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488195</v>
       </c>
       <c r="B54" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488215</v>
       </c>
       <c r="B55" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488233</v>
       </c>
       <c r="B56" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>136488247</v>
       </c>
       <c r="B119" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>136488262</v>
       </c>
       <c r="B120" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>134851616</v>
       </c>
       <c r="B121" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>134851532</v>
       </c>
       <c r="B144" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>136488052</v>
       </c>
       <c r="B188" t="n">
-        <v>90880</v>
+        <v>90882</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>136487945</v>
       </c>
       <c r="B189" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134851705</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134851657</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>136487855</v>
       </c>
       <c r="B51" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136488085</v>
       </c>
       <c r="B52" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488093</v>
       </c>
       <c r="B53" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488195</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488215</v>
       </c>
       <c r="B55" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488233</v>
       </c>
       <c r="B56" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>136488052</v>
       </c>
       <c r="B188" t="n">
-        <v>90882</v>
+        <v>90884</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>136487945</v>
       </c>
       <c r="B189" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ189"/>
+  <dimension ref="A1:AZ190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4902,45 +4902,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129512476</v>
+        <v>136934641</v>
       </c>
       <c r="B42" t="n">
-        <v>80433</v>
+        <v>93427</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494654</v>
+        <v>494265</v>
       </c>
       <c r="R42" t="n">
-        <v>6833987</v>
+        <v>6834642</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4967,12 +4970,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4981,30 +4984,31 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512476</t>
+          <t>https://artportalen.se/Sighting/136934641</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129521656</v>
+        <v>129512476</v>
       </c>
       <c r="B43" t="n">
         <v>80433</v>
@@ -5039,13 +5043,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494219</v>
+        <v>494654</v>
       </c>
       <c r="R43" t="n">
-        <v>6834291</v>
+        <v>6833987</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5069,12 +5073,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5100,13 +5104,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521656</t>
+          <t>https://artportalen.se/Sighting/129512476</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129521826</v>
+        <v>129521656</v>
       </c>
       <c r="B44" t="n">
         <v>80433</v>
@@ -5137,17 +5141,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494361</v>
+        <v>494219</v>
       </c>
       <c r="R44" t="n">
-        <v>6834336</v>
+        <v>6834291</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5191,24 +5195,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521826</t>
+          <t>https://artportalen.se/Sighting/129521656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129521986</v>
+        <v>129521826</v>
       </c>
       <c r="B45" t="n">
         <v>80433</v>
@@ -5239,14 +5243,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494336</v>
+        <v>494361</v>
       </c>
       <c r="R45" t="n">
-        <v>6834146</v>
+        <v>6834336</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,24 +5297,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521986</t>
+          <t>https://artportalen.se/Sighting/129521826</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522027</v>
+        <v>129521986</v>
       </c>
       <c r="B46" t="n">
         <v>80433</v>
@@ -5345,10 +5349,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494337</v>
+        <v>494336</v>
       </c>
       <c r="R46" t="n">
-        <v>6834149</v>
+        <v>6834146</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5406,13 +5410,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522027</t>
+          <t>https://artportalen.se/Sighting/129521986</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524122</v>
+        <v>129522027</v>
       </c>
       <c r="B47" t="n">
         <v>80433</v>
@@ -5447,10 +5451,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494556</v>
+        <v>494337</v>
       </c>
       <c r="R47" t="n">
-        <v>6834468</v>
+        <v>6834149</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5508,13 +5512,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524122</t>
+          <t>https://artportalen.se/Sighting/129522027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129524667</v>
+        <v>129524122</v>
       </c>
       <c r="B48" t="n">
         <v>80433</v>
@@ -5542,26 +5546,17 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494352</v>
+        <v>494556</v>
       </c>
       <c r="R48" t="n">
-        <v>6834596</v>
+        <v>6834468</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5608,27 +5603,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524667</t>
+          <t>https://artportalen.se/Sighting/129524122</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129524392</v>
+        <v>129524667</v>
       </c>
       <c r="B49" t="n">
-        <v>93197</v>
+        <v>80433</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5636,34 +5631,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494486</v>
+        <v>494352</v>
       </c>
       <c r="R49" t="n">
-        <v>6834613</v>
+        <v>6834596</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5710,24 +5714,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524392</t>
+          <t>https://artportalen.se/Sighting/129524667</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524797</v>
+        <v>129524392</v>
       </c>
       <c r="B50" t="n">
         <v>93197</v>
@@ -5755,31 +5759,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494387</v>
+        <v>494486</v>
       </c>
       <c r="R50" t="n">
-        <v>6834437</v>
+        <v>6834613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5826,27 +5816,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524797</t>
+          <t>https://artportalen.se/Sighting/129524392</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136487855</v>
+        <v>129524797</v>
       </c>
       <c r="B51" t="n">
-        <v>93411</v>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,20 +5861,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494552</v>
+        <v>494387</v>
       </c>
       <c r="R51" t="n">
-        <v>6834642</v>
+        <v>6834437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5911,12 +5912,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5925,31 +5926,30 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136487855</t>
+          <t>https://artportalen.se/Sighting/129524797</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136488085</v>
+        <v>136487855</v>
       </c>
       <c r="B52" t="n">
         <v>93411</v>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494453</v>
+        <v>494552</v>
       </c>
       <c r="R52" t="n">
-        <v>6834545</v>
+        <v>6834642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6049,13 +6049,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488085</t>
+          <t>https://artportalen.se/Sighting/136487855</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136488093</v>
+        <v>136488085</v>
       </c>
       <c r="B53" t="n">
         <v>93411</v>
@@ -6096,7 +6096,7 @@
         <v>494453</v>
       </c>
       <c r="R53" t="n">
-        <v>6834484</v>
+        <v>6834545</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6155,13 +6155,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488093</t>
+          <t>https://artportalen.se/Sighting/136488085</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136488195</v>
+        <v>136488093</v>
       </c>
       <c r="B54" t="n">
         <v>93411</v>
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494207</v>
+        <v>494453</v>
       </c>
       <c r="R54" t="n">
-        <v>6834641</v>
+        <v>6834484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6261,13 +6261,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488195</t>
+          <t>https://artportalen.se/Sighting/136488093</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136488215</v>
+        <v>136488195</v>
       </c>
       <c r="B55" t="n">
         <v>93411</v>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494139</v>
+        <v>494207</v>
       </c>
       <c r="R55" t="n">
-        <v>6834574</v>
+        <v>6834641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6367,13 +6367,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488215</t>
+          <t>https://artportalen.se/Sighting/136488195</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136488233</v>
+        <v>136488215</v>
       </c>
       <c r="B56" t="n">
         <v>93411</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494324</v>
+        <v>494139</v>
       </c>
       <c r="R56" t="n">
-        <v>6834000</v>
+        <v>6834574</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6473,16 +6473,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488233</t>
+          <t>https://artportalen.se/Sighting/136488215</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521664</v>
+        <v>136488233</v>
       </c>
       <c r="B57" t="n">
-        <v>91930</v>
+        <v>93411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6490,34 +6490,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494255</v>
+        <v>494324</v>
       </c>
       <c r="R57" t="n">
-        <v>6834250</v>
+        <v>6834000</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6544,12 +6547,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6558,30 +6561,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521664</t>
+          <t>https://artportalen.se/Sighting/136488233</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522736</v>
+        <v>129521664</v>
       </c>
       <c r="B58" t="n">
         <v>91930</v>
@@ -6612,14 +6616,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494443</v>
+        <v>494255</v>
       </c>
       <c r="R58" t="n">
-        <v>6834230</v>
+        <v>6834250</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6666,65 +6670,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522736</t>
+          <t>https://artportalen.se/Sighting/129521664</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121463373</v>
+        <v>129522736</v>
       </c>
       <c r="B59" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494068</v>
+        <v>494443</v>
       </c>
       <c r="R59" t="n">
-        <v>6834592</v>
+        <v>6834230</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6748,22 +6752,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6778,65 +6772,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463373</t>
+          <t>https://artportalen.se/Sighting/129522736</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121313238</v>
+        <v>121463373</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493815</v>
+        <v>494068</v>
       </c>
       <c r="R60" t="n">
-        <v>6834929</v>
+        <v>6834592</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6860,12 +6854,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6880,24 +6884,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313238</t>
+          <t>https://artportalen.se/Sighting/121463373</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121462834</v>
+        <v>121313238</v>
       </c>
       <c r="B61" t="n">
         <v>79327</v>
@@ -6928,17 +6932,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494009</v>
+        <v>493815</v>
       </c>
       <c r="R61" t="n">
-        <v>6834570</v>
+        <v>6834929</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6962,27 +6966,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6997,24 +6986,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121462834</t>
+          <t>https://artportalen.se/Sighting/121313238</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121463067</v>
+        <v>121462834</v>
       </c>
       <c r="B62" t="n">
         <v>79327</v>
@@ -7049,10 +7038,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493995</v>
+        <v>494009</v>
       </c>
       <c r="R62" t="n">
-        <v>6834619</v>
+        <v>6834570</v>
       </c>
       <c r="S62" t="n">
         <v>9</v>
@@ -7084,7 +7073,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7094,12 +7083,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7125,13 +7114,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463067</t>
+          <t>https://artportalen.se/Sighting/121462834</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121463429</v>
+        <v>121463067</v>
       </c>
       <c r="B63" t="n">
         <v>79327</v>
@@ -7166,10 +7155,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494075</v>
+        <v>493995</v>
       </c>
       <c r="R63" t="n">
-        <v>6834606</v>
+        <v>6834619</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -7201,7 +7190,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7211,12 +7200,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7242,13 +7231,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463429</t>
+          <t>https://artportalen.se/Sighting/121463067</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121463770</v>
+        <v>121463429</v>
       </c>
       <c r="B64" t="n">
         <v>79327</v>
@@ -7283,10 +7272,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494125</v>
+        <v>494075</v>
       </c>
       <c r="R64" t="n">
-        <v>6834588</v>
+        <v>6834606</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -7318,7 +7307,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7328,12 +7317,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7353,19 +7342,19 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anders Heggestad, Lisa Olson, Lars-Erik Nilsson, Göran Ehn</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463770</t>
+          <t>https://artportalen.se/Sighting/121463429</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129511911</v>
+        <v>121463770</v>
       </c>
       <c r="B65" t="n">
         <v>79327</v>
@@ -7400,13 +7389,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494614</v>
+        <v>494125</v>
       </c>
       <c r="R65" t="n">
-        <v>6834378</v>
+        <v>6834588</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7430,12 +7419,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7450,24 +7454,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens, Anders Heggestad, Lisa Olson, Lars-Erik Nilsson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511911</t>
+          <t>https://artportalen.se/Sighting/121463770</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129511957</v>
+        <v>129511911</v>
       </c>
       <c r="B66" t="n">
         <v>79327</v>
@@ -7502,10 +7506,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494635</v>
+        <v>494614</v>
       </c>
       <c r="R66" t="n">
-        <v>6834347</v>
+        <v>6834378</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7563,13 +7567,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511957</t>
+          <t>https://artportalen.se/Sighting/129511911</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129511985</v>
+        <v>129511957</v>
       </c>
       <c r="B67" t="n">
         <v>79327</v>
@@ -7604,10 +7608,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494672</v>
+        <v>494635</v>
       </c>
       <c r="R67" t="n">
-        <v>6834352</v>
+        <v>6834347</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7665,13 +7669,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511985</t>
+          <t>https://artportalen.se/Sighting/129511957</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129512105</v>
+        <v>129511985</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7706,10 +7710,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494664</v>
+        <v>494672</v>
       </c>
       <c r="R68" t="n">
-        <v>6834295</v>
+        <v>6834352</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7767,13 +7771,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512105</t>
+          <t>https://artportalen.se/Sighting/129511985</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129512125</v>
+        <v>129512105</v>
       </c>
       <c r="B69" t="n">
         <v>79327</v>
@@ -7808,10 +7812,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494678</v>
+        <v>494664</v>
       </c>
       <c r="R69" t="n">
-        <v>6834243</v>
+        <v>6834295</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7869,13 +7873,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512125</t>
+          <t>https://artportalen.se/Sighting/129512105</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129512195</v>
+        <v>129512125</v>
       </c>
       <c r="B70" t="n">
         <v>79327</v>
@@ -7910,10 +7914,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494612</v>
+        <v>494678</v>
       </c>
       <c r="R70" t="n">
-        <v>6834233</v>
+        <v>6834243</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7971,13 +7975,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512195</t>
+          <t>https://artportalen.se/Sighting/129512125</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129512298</v>
+        <v>129512195</v>
       </c>
       <c r="B71" t="n">
         <v>79327</v>
@@ -8012,10 +8016,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494611</v>
+        <v>494612</v>
       </c>
       <c r="R71" t="n">
-        <v>6834107</v>
+        <v>6834233</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8073,13 +8077,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512298</t>
+          <t>https://artportalen.se/Sighting/129512195</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129512361</v>
+        <v>129512298</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8114,10 +8118,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494634</v>
+        <v>494611</v>
       </c>
       <c r="R72" t="n">
-        <v>6834067</v>
+        <v>6834107</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8175,13 +8179,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512361</t>
+          <t>https://artportalen.se/Sighting/129512298</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129512658</v>
+        <v>129512361</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8216,10 +8220,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494506</v>
+        <v>494634</v>
       </c>
       <c r="R73" t="n">
-        <v>6834042</v>
+        <v>6834067</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8277,13 +8281,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512658</t>
+          <t>https://artportalen.se/Sighting/129512361</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129512676</v>
+        <v>129512658</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8318,10 +8322,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494500</v>
+        <v>494506</v>
       </c>
       <c r="R74" t="n">
-        <v>6834016</v>
+        <v>6834042</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8379,13 +8383,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512676</t>
+          <t>https://artportalen.se/Sighting/129512658</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129512771</v>
+        <v>129512676</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8424,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494466</v>
+        <v>494500</v>
       </c>
       <c r="R75" t="n">
-        <v>6833989</v>
+        <v>6834016</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8481,13 +8485,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512771</t>
+          <t>https://artportalen.se/Sighting/129512676</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129512788</v>
+        <v>129512771</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8522,10 +8526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494465</v>
+        <v>494466</v>
       </c>
       <c r="R76" t="n">
-        <v>6833963</v>
+        <v>6833989</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8583,13 +8587,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512788</t>
+          <t>https://artportalen.se/Sighting/129512771</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129512918</v>
+        <v>129512788</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8624,10 +8628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494417</v>
+        <v>494465</v>
       </c>
       <c r="R77" t="n">
-        <v>6833948</v>
+        <v>6833963</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8685,13 +8689,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512918</t>
+          <t>https://artportalen.se/Sighting/129512788</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129513122</v>
+        <v>129512918</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8726,10 +8730,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494490</v>
+        <v>494417</v>
       </c>
       <c r="R78" t="n">
-        <v>6834127</v>
+        <v>6833948</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8787,13 +8791,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513122</t>
+          <t>https://artportalen.se/Sighting/129512918</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129513342</v>
+        <v>129513122</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8828,10 +8832,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494384</v>
+        <v>494490</v>
       </c>
       <c r="R79" t="n">
-        <v>6834354</v>
+        <v>6834127</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8889,13 +8893,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513342</t>
+          <t>https://artportalen.se/Sighting/129513122</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129513370</v>
+        <v>129513342</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8930,10 +8934,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494369</v>
+        <v>494384</v>
       </c>
       <c r="R80" t="n">
-        <v>6834380</v>
+        <v>6834354</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8991,13 +8995,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513370</t>
+          <t>https://artportalen.se/Sighting/129513342</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129513412</v>
+        <v>129513370</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9032,10 +9036,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494427</v>
+        <v>494369</v>
       </c>
       <c r="R81" t="n">
-        <v>6834434</v>
+        <v>6834380</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9093,13 +9097,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513412</t>
+          <t>https://artportalen.se/Sighting/129513370</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129513741</v>
+        <v>129513412</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9134,10 +9138,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494548</v>
+        <v>494427</v>
       </c>
       <c r="R82" t="n">
-        <v>6834603</v>
+        <v>6834434</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9195,13 +9199,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513741</t>
+          <t>https://artportalen.se/Sighting/129513412</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129513963</v>
+        <v>129513741</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9232,14 +9236,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494311</v>
+        <v>494548</v>
       </c>
       <c r="R83" t="n">
-        <v>6834701</v>
+        <v>6834603</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9297,13 +9301,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513963</t>
+          <t>https://artportalen.se/Sighting/129513741</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129520902</v>
+        <v>129513963</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9334,14 +9338,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494278</v>
+        <v>494311</v>
       </c>
       <c r="R84" t="n">
-        <v>6834456</v>
+        <v>6834701</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9368,12 +9372,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9388,24 +9392,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520902</t>
+          <t>https://artportalen.se/Sighting/129513963</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129520912</v>
+        <v>129520902</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9436,14 +9440,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494290</v>
+        <v>494278</v>
       </c>
       <c r="R85" t="n">
-        <v>6834454</v>
+        <v>6834456</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9490,24 +9494,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520912</t>
+          <t>https://artportalen.se/Sighting/129520902</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129520952</v>
+        <v>129520912</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9542,7 +9546,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494291</v>
+        <v>494290</v>
       </c>
       <c r="R86" t="n">
         <v>6834454</v>
@@ -9603,13 +9607,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520952</t>
+          <t>https://artportalen.se/Sighting/129520912</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129521002</v>
+        <v>129520952</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9640,14 +9644,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494241</v>
+        <v>494291</v>
       </c>
       <c r="R87" t="n">
-        <v>6834425</v>
+        <v>6834454</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9694,24 +9698,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521002</t>
+          <t>https://artportalen.se/Sighting/129520952</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521072</v>
+        <v>129521002</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9746,10 +9750,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494234</v>
+        <v>494241</v>
       </c>
       <c r="R88" t="n">
-        <v>6834416</v>
+        <v>6834425</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9807,13 +9811,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521072</t>
+          <t>https://artportalen.se/Sighting/129521002</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521144</v>
+        <v>129521072</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9848,10 +9852,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494222</v>
+        <v>494234</v>
       </c>
       <c r="R89" t="n">
-        <v>6834390</v>
+        <v>6834416</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9909,13 +9913,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521144</t>
+          <t>https://artportalen.se/Sighting/129521072</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129521147</v>
+        <v>129521144</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -9946,14 +9950,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494225</v>
+        <v>494222</v>
       </c>
       <c r="R90" t="n">
-        <v>6834382</v>
+        <v>6834390</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10000,24 +10004,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521147</t>
+          <t>https://artportalen.se/Sighting/129521144</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129521302</v>
+        <v>129521147</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10048,17 +10052,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494215</v>
+        <v>494225</v>
       </c>
       <c r="R91" t="n">
-        <v>6834362</v>
+        <v>6834382</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10102,24 +10106,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521302</t>
+          <t>https://artportalen.se/Sighting/129521147</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129521418</v>
+        <v>129521302</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10150,17 +10154,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494176</v>
+        <v>494215</v>
       </c>
       <c r="R92" t="n">
-        <v>6834368</v>
+        <v>6834362</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10204,24 +10208,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521418</t>
+          <t>https://artportalen.se/Sighting/129521302</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129521804</v>
+        <v>129521418</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10252,17 +10256,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494297</v>
+        <v>494176</v>
       </c>
       <c r="R93" t="n">
-        <v>6834314</v>
+        <v>6834368</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10306,24 +10310,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521804</t>
+          <t>https://artportalen.se/Sighting/129521418</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521823</v>
+        <v>129521804</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10354,17 +10358,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494360</v>
+        <v>494297</v>
       </c>
       <c r="R94" t="n">
-        <v>6834206</v>
+        <v>6834314</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10408,24 +10412,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521823</t>
+          <t>https://artportalen.se/Sighting/129521804</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521967</v>
+        <v>129521823</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10456,17 +10460,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494346</v>
+        <v>494360</v>
       </c>
       <c r="R95" t="n">
-        <v>6834277</v>
+        <v>6834206</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10510,24 +10514,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521967</t>
+          <t>https://artportalen.se/Sighting/129521823</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129522129</v>
+        <v>129521967</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10558,14 +10562,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494397</v>
+        <v>494346</v>
       </c>
       <c r="R96" t="n">
-        <v>6834116</v>
+        <v>6834277</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10612,24 +10616,24 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522129</t>
+          <t>https://artportalen.se/Sighting/129521967</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129522450</v>
+        <v>129522129</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10660,17 +10664,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494325</v>
+        <v>494397</v>
       </c>
       <c r="R97" t="n">
-        <v>6834177</v>
+        <v>6834116</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10714,24 +10718,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522450</t>
+          <t>https://artportalen.se/Sighting/129522129</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10762,17 +10766,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R98" t="n">
         <v>6834177</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10816,24 +10820,24 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522454</t>
+          <t>https://artportalen.se/Sighting/129522450</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129522706</v>
+        <v>129522454</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -10864,17 +10868,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494454</v>
+        <v>494456</v>
       </c>
       <c r="R99" t="n">
-        <v>6834225</v>
+        <v>6834177</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10918,24 +10922,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522706</t>
+          <t>https://artportalen.se/Sighting/129522454</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129522819</v>
+        <v>129522706</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -10970,13 +10974,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494470</v>
+        <v>494454</v>
       </c>
       <c r="R100" t="n">
-        <v>6834231</v>
+        <v>6834225</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11031,13 +11035,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522819</t>
+          <t>https://artportalen.se/Sighting/129522706</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129522857</v>
+        <v>129522819</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11072,10 +11076,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494475</v>
+        <v>494470</v>
       </c>
       <c r="R101" t="n">
-        <v>6834232</v>
+        <v>6834231</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11133,13 +11137,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522857</t>
+          <t>https://artportalen.se/Sighting/129522819</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522903</v>
+        <v>129522857</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11174,10 +11178,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494466</v>
+        <v>494475</v>
       </c>
       <c r="R102" t="n">
-        <v>6834211</v>
+        <v>6834232</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11235,13 +11239,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522903</t>
+          <t>https://artportalen.se/Sighting/129522857</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129523005</v>
+        <v>129522903</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11276,10 +11280,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494491</v>
+        <v>494466</v>
       </c>
       <c r="R103" t="n">
-        <v>6834229</v>
+        <v>6834211</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11337,13 +11341,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523005</t>
+          <t>https://artportalen.se/Sighting/129522903</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129523011</v>
+        <v>129523005</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11374,14 +11378,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494480</v>
+        <v>494491</v>
       </c>
       <c r="R104" t="n">
-        <v>6834232</v>
+        <v>6834229</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11428,24 +11432,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523011</t>
+          <t>https://artportalen.se/Sighting/129523005</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129524130</v>
+        <v>129523011</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11480,10 +11484,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494537</v>
+        <v>494480</v>
       </c>
       <c r="R105" t="n">
-        <v>6834492</v>
+        <v>6834232</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11541,13 +11545,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524130</t>
+          <t>https://artportalen.se/Sighting/129523011</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129524189</v>
+        <v>129524130</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11578,17 +11582,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494606</v>
+        <v>494537</v>
       </c>
       <c r="R106" t="n">
-        <v>6834497</v>
+        <v>6834492</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11632,24 +11636,24 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524189</t>
+          <t>https://artportalen.se/Sighting/129524130</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129524246</v>
+        <v>129524189</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -11684,13 +11688,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494560</v>
+        <v>494606</v>
       </c>
       <c r="R107" t="n">
-        <v>6834565</v>
+        <v>6834497</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11745,13 +11749,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524246</t>
+          <t>https://artportalen.se/Sighting/129524189</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129524342</v>
+        <v>129524246</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -11786,13 +11790,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494544</v>
+        <v>494560</v>
       </c>
       <c r="R108" t="n">
-        <v>6834616</v>
+        <v>6834565</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11847,13 +11851,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524342</t>
+          <t>https://artportalen.se/Sighting/129524246</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129524381</v>
+        <v>129524342</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -11884,17 +11888,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494485</v>
+        <v>494544</v>
       </c>
       <c r="R109" t="n">
-        <v>6834612</v>
+        <v>6834616</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11938,24 +11942,24 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524381</t>
+          <t>https://artportalen.se/Sighting/129524342</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129524385</v>
+        <v>129524381</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -11986,17 +11990,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494528</v>
+        <v>494485</v>
       </c>
       <c r="R110" t="n">
-        <v>6834660</v>
+        <v>6834612</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12040,24 +12044,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524385</t>
+          <t>https://artportalen.se/Sighting/129524381</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129524525</v>
+        <v>129524385</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12088,17 +12092,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494354</v>
+        <v>494528</v>
       </c>
       <c r="R111" t="n">
-        <v>6834662</v>
+        <v>6834660</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12142,24 +12146,24 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524525</t>
+          <t>https://artportalen.se/Sighting/129524385</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129524530</v>
+        <v>129524525</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12190,14 +12194,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494349</v>
+        <v>494354</v>
       </c>
       <c r="R112" t="n">
-        <v>6834653</v>
+        <v>6834662</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12244,24 +12248,24 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524530</t>
+          <t>https://artportalen.se/Sighting/129524525</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524747</v>
+        <v>129524530</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12292,14 +12296,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494401</v>
+        <v>494349</v>
       </c>
       <c r="R113" t="n">
-        <v>6834640</v>
+        <v>6834653</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12346,24 +12350,24 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524747</t>
+          <t>https://artportalen.se/Sighting/129524530</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524762</v>
+        <v>129524747</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12394,14 +12398,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494406</v>
+        <v>494401</v>
       </c>
       <c r="R114" t="n">
-        <v>6834477</v>
+        <v>6834640</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12448,24 +12452,24 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524762</t>
+          <t>https://artportalen.se/Sighting/129524747</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524775</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12500,10 +12504,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494416</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834464</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12561,13 +12565,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524775</t>
+          <t>https://artportalen.se/Sighting/129524762</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524779</v>
+        <v>129524775</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -12602,10 +12606,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494423</v>
+        <v>494416</v>
       </c>
       <c r="R116" t="n">
-        <v>6834463</v>
+        <v>6834464</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12663,13 +12667,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524779</t>
+          <t>https://artportalen.se/Sighting/129524775</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524785</v>
+        <v>129524779</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -12704,10 +12708,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494405</v>
+        <v>494423</v>
       </c>
       <c r="R117" t="n">
-        <v>6834446</v>
+        <v>6834463</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12765,13 +12769,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524785</t>
+          <t>https://artportalen.se/Sighting/129524779</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129524791</v>
+        <v>129524785</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -12806,10 +12810,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494381</v>
+        <v>494405</v>
       </c>
       <c r="R118" t="n">
-        <v>6834429</v>
+        <v>6834446</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12867,16 +12871,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524791</t>
+          <t>https://artportalen.se/Sighting/129524785</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>136488247</v>
+        <v>129524791</v>
       </c>
       <c r="B119" t="n">
-        <v>79476</v>
+        <v>79327</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12902,19 +12906,16 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494507</v>
+        <v>494381</v>
       </c>
       <c r="R119" t="n">
-        <v>6833914</v>
+        <v>6834429</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12941,12 +12942,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12955,31 +12956,30 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488247</t>
+          <t>https://artportalen.se/Sighting/129524791</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136488262</v>
+        <v>136488247</v>
       </c>
       <c r="B120" t="n">
         <v>79476</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494332</v>
+        <v>494507</v>
       </c>
       <c r="R120" t="n">
-        <v>6834191</v>
+        <v>6833914</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13079,38 +13079,38 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488262</t>
+          <t>https://artportalen.se/Sighting/136488247</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134851616</v>
+        <v>136488262</v>
       </c>
       <c r="B121" t="n">
-        <v>79500</v>
+        <v>79476</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13123,10 +13123,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494545</v>
+        <v>494332</v>
       </c>
       <c r="R121" t="n">
-        <v>6834524</v>
+        <v>6834191</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13185,54 +13185,57 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134851616</t>
+          <t>https://artportalen.se/Sighting/136488262</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121463076</v>
+        <v>134851616</v>
       </c>
       <c r="B122" t="n">
-        <v>83307</v>
+        <v>79500</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494009</v>
+        <v>494545</v>
       </c>
       <c r="R122" t="n">
-        <v>6834588</v>
+        <v>6834524</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13256,22 +13259,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13280,33 +13273,34 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463076</t>
+          <t>https://artportalen.se/Sighting/134851616</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129520975</v>
+        <v>121463076</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13314,34 +13308,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494243</v>
+        <v>494009</v>
       </c>
       <c r="R123" t="n">
-        <v>6834445</v>
+        <v>6834588</v>
       </c>
       <c r="S123" t="n">
         <v>20</v>
@@ -13368,12 +13362,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13388,24 +13392,24 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520975</t>
+          <t>https://artportalen.se/Sighting/121463076</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522151</v>
+        <v>129520975</v>
       </c>
       <c r="B124" t="n">
         <v>79084</v>
@@ -13440,13 +13444,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494385</v>
+        <v>494243</v>
       </c>
       <c r="R124" t="n">
-        <v>6834229</v>
+        <v>6834445</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13501,13 +13505,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522151</t>
+          <t>https://artportalen.se/Sighting/129520975</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522341</v>
+        <v>129522151</v>
       </c>
       <c r="B125" t="n">
         <v>79084</v>
@@ -13542,10 +13546,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494345</v>
+        <v>494385</v>
       </c>
       <c r="R125" t="n">
-        <v>6834202</v>
+        <v>6834229</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13603,16 +13607,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522341</t>
+          <t>https://artportalen.se/Sighting/129522151</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121313133</v>
+        <v>129522341</v>
       </c>
       <c r="B126" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13620,37 +13624,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>493849</v>
+        <v>494345</v>
       </c>
       <c r="R126" t="n">
-        <v>6834871</v>
+        <v>6834202</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13674,17 +13678,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13699,24 +13698,24 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313133</t>
+          <t>https://artportalen.se/Sighting/129522341</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121313322</v>
+        <v>121313133</v>
       </c>
       <c r="B127" t="n">
         <v>80432</v>
@@ -13751,13 +13750,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>493813</v>
+        <v>493849</v>
       </c>
       <c r="R127" t="n">
-        <v>6834953</v>
+        <v>6834871</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13787,6 +13786,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13801,24 +13805,24 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313322</t>
+          <t>https://artportalen.se/Sighting/121313133</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129512470</v>
+        <v>121313322</v>
       </c>
       <c r="B128" t="n">
         <v>80432</v>
@@ -13849,17 +13853,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494652</v>
+        <v>493813</v>
       </c>
       <c r="R128" t="n">
-        <v>6833984</v>
+        <v>6834953</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13883,12 +13887,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13914,13 +13918,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512470</t>
+          <t>https://artportalen.se/Sighting/121313322</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129512549</v>
+        <v>129512470</v>
       </c>
       <c r="B129" t="n">
         <v>80432</v>
@@ -13955,10 +13959,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494625</v>
+        <v>494652</v>
       </c>
       <c r="R129" t="n">
-        <v>6834032</v>
+        <v>6833984</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14016,13 +14020,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512549</t>
+          <t>https://artportalen.se/Sighting/129512470</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129521092</v>
+        <v>129512549</v>
       </c>
       <c r="B130" t="n">
         <v>80432</v>
@@ -14057,10 +14061,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494222</v>
+        <v>494625</v>
       </c>
       <c r="R130" t="n">
-        <v>6834398</v>
+        <v>6834032</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14087,12 +14091,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14118,13 +14122,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521092</t>
+          <t>https://artportalen.se/Sighting/129512549</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129521874</v>
+        <v>129521092</v>
       </c>
       <c r="B131" t="n">
         <v>80432</v>
@@ -14155,14 +14159,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494355</v>
+        <v>494222</v>
       </c>
       <c r="R131" t="n">
-        <v>6834295</v>
+        <v>6834398</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14209,24 +14213,24 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521874</t>
+          <t>https://artportalen.se/Sighting/129521092</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521977</v>
+        <v>129521874</v>
       </c>
       <c r="B132" t="n">
         <v>80432</v>
@@ -14257,14 +14261,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494334</v>
+        <v>494355</v>
       </c>
       <c r="R132" t="n">
-        <v>6834144</v>
+        <v>6834295</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14311,24 +14315,24 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521977</t>
+          <t>https://artportalen.se/Sighting/129521874</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129522012</v>
+        <v>129521977</v>
       </c>
       <c r="B133" t="n">
         <v>80432</v>
@@ -14363,10 +14367,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494337</v>
+        <v>494334</v>
       </c>
       <c r="R133" t="n">
-        <v>6834146</v>
+        <v>6834144</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14424,13 +14428,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522012</t>
+          <t>https://artportalen.se/Sighting/129521977</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129522173</v>
+        <v>129522012</v>
       </c>
       <c r="B134" t="n">
         <v>80432</v>
@@ -14465,10 +14469,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494418</v>
+        <v>494337</v>
       </c>
       <c r="R134" t="n">
-        <v>6834113</v>
+        <v>6834146</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14526,13 +14530,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522173</t>
+          <t>https://artportalen.se/Sighting/129522012</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129524119</v>
+        <v>129522173</v>
       </c>
       <c r="B135" t="n">
         <v>80432</v>
@@ -14567,10 +14571,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494556</v>
+        <v>494418</v>
       </c>
       <c r="R135" t="n">
-        <v>6834468</v>
+        <v>6834113</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14628,13 +14632,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524119</t>
+          <t>https://artportalen.se/Sighting/129522173</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524581</v>
+        <v>129524119</v>
       </c>
       <c r="B136" t="n">
         <v>80432</v>
@@ -14665,14 +14669,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494323</v>
+        <v>494556</v>
       </c>
       <c r="R136" t="n">
-        <v>6834627</v>
+        <v>6834468</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14719,24 +14723,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524581</t>
+          <t>https://artportalen.se/Sighting/129524119</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524595</v>
+        <v>129524581</v>
       </c>
       <c r="B137" t="n">
         <v>80432</v>
@@ -14771,10 +14775,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494349</v>
+        <v>494323</v>
       </c>
       <c r="R137" t="n">
-        <v>6834611</v>
+        <v>6834627</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14832,13 +14836,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524595</t>
+          <t>https://artportalen.se/Sighting/129524581</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129524606</v>
+        <v>129524595</v>
       </c>
       <c r="B138" t="n">
         <v>80432</v>
@@ -14873,10 +14877,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494333</v>
+        <v>494349</v>
       </c>
       <c r="R138" t="n">
-        <v>6834609</v>
+        <v>6834611</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14934,13 +14938,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524606</t>
+          <t>https://artportalen.se/Sighting/129524595</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129524680</v>
+        <v>129524606</v>
       </c>
       <c r="B139" t="n">
         <v>80432</v>
@@ -14975,10 +14979,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>494357</v>
+        <v>494333</v>
       </c>
       <c r="R139" t="n">
-        <v>6834592</v>
+        <v>6834609</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15036,54 +15040,54 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524680</t>
+          <t>https://artportalen.se/Sighting/129524606</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121313317</v>
+        <v>129524680</v>
       </c>
       <c r="B140" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>493813</v>
+        <v>494357</v>
       </c>
       <c r="R140" t="n">
-        <v>6834953</v>
+        <v>6834592</v>
       </c>
       <c r="S140" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15107,12 +15111,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15127,24 +15131,24 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313317</t>
+          <t>https://artportalen.se/Sighting/129524680</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129521887</v>
+        <v>121313317</v>
       </c>
       <c r="B141" t="n">
         <v>80461</v>
@@ -15175,17 +15179,17 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>494350</v>
+        <v>493813</v>
       </c>
       <c r="R141" t="n">
-        <v>6834298</v>
+        <v>6834953</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15209,12 +15213,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15229,27 +15233,27 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521887</t>
+          <t>https://artportalen.se/Sighting/121313317</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129512556</v>
+        <v>129521887</v>
       </c>
       <c r="B142" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15257,34 +15261,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>494625</v>
+        <v>494350</v>
       </c>
       <c r="R142" t="n">
-        <v>6834033</v>
+        <v>6834298</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15311,12 +15315,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15331,62 +15335,62 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512556</t>
+          <t>https://artportalen.se/Sighting/129521887</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129523028</v>
+        <v>129512556</v>
       </c>
       <c r="B143" t="n">
-        <v>78334</v>
+        <v>80468</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R143" t="n">
-        <v>6834263</v>
+        <v>6834033</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15413,12 +15417,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15433,70 +15437,62 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523028</t>
+          <t>https://artportalen.se/Sighting/129512556</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134851532</v>
+        <v>129523028</v>
       </c>
       <c r="B144" t="n">
-        <v>58005</v>
+        <v>78334</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>494480</v>
+        <v>494500</v>
       </c>
       <c r="R144" t="n">
-        <v>6834438</v>
+        <v>6834263</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15523,12 +15519,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15543,27 +15539,27 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134851532</t>
+          <t>https://artportalen.se/Sighting/129523028</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129522100</v>
+        <v>134851532</v>
       </c>
       <c r="B145" t="n">
-        <v>58327</v>
+        <v>58005</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15571,16 +15567,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -15589,19 +15585,27 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>494368</v>
+        <v>494480</v>
       </c>
       <c r="R145" t="n">
-        <v>6834126</v>
+        <v>6834438</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15625,12 +15629,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15645,49 +15649,49 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522100</t>
+          <t>https://artportalen.se/Sighting/134851532</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129522021</v>
+        <v>129522100</v>
       </c>
       <c r="B146" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15697,10 +15701,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>494337</v>
+        <v>494368</v>
       </c>
       <c r="R146" t="n">
-        <v>6834149</v>
+        <v>6834126</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15758,13 +15762,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522021</t>
+          <t>https://artportalen.se/Sighting/129522100</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129523899</v>
+        <v>129522021</v>
       </c>
       <c r="B147" t="n">
         <v>58114</v>
@@ -15799,10 +15803,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>494543</v>
+        <v>494337</v>
       </c>
       <c r="R147" t="n">
-        <v>6834251</v>
+        <v>6834149</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15860,51 +15864,51 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523899</t>
+          <t>https://artportalen.se/Sighting/129522021</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121314344</v>
+        <v>129523899</v>
       </c>
       <c r="B148" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>493875</v>
+        <v>494543</v>
       </c>
       <c r="R148" t="n">
-        <v>6834814</v>
+        <v>6834251</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15931,12 +15935,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15951,24 +15955,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121314344</t>
+          <t>https://artportalen.se/Sighting/129523899</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121314972</v>
+        <v>121314344</v>
       </c>
       <c r="B149" t="n">
         <v>99118</v>
@@ -16003,10 +16007,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>493938</v>
+        <v>493875</v>
       </c>
       <c r="R149" t="n">
-        <v>6834637</v>
+        <v>6834814</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16064,13 +16068,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121314972</t>
+          <t>https://artportalen.se/Sighting/121314344</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121315050</v>
+        <v>121314972</v>
       </c>
       <c r="B150" t="n">
         <v>99118</v>
@@ -16105,10 +16109,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>493937</v>
+        <v>493938</v>
       </c>
       <c r="R150" t="n">
-        <v>6834639</v>
+        <v>6834637</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16166,13 +16170,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315050</t>
+          <t>https://artportalen.se/Sighting/121314972</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121315126</v>
+        <v>121315050</v>
       </c>
       <c r="B151" t="n">
         <v>99118</v>
@@ -16207,13 +16211,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>493940</v>
+        <v>493937</v>
       </c>
       <c r="R151" t="n">
-        <v>6834631</v>
+        <v>6834639</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16243,11 +16247,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16273,13 +16272,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315126</t>
+          <t>https://artportalen.se/Sighting/121315050</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121315885</v>
+        <v>121315126</v>
       </c>
       <c r="B152" t="n">
         <v>99118</v>
@@ -16314,13 +16313,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>493917</v>
+        <v>493940</v>
       </c>
       <c r="R152" t="n">
-        <v>6834746</v>
+        <v>6834631</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16350,6 +16349,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16375,13 +16379,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315885</t>
+          <t>https://artportalen.se/Sighting/121315126</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121316014</v>
+        <v>121315885</v>
       </c>
       <c r="B153" t="n">
         <v>99118</v>
@@ -16416,10 +16420,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>493896</v>
+        <v>493917</v>
       </c>
       <c r="R153" t="n">
-        <v>6834747</v>
+        <v>6834746</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16477,13 +16481,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316014</t>
+          <t>https://artportalen.se/Sighting/121315885</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121316066</v>
+        <v>121316014</v>
       </c>
       <c r="B154" t="n">
         <v>99118</v>
@@ -16521,7 +16525,7 @@
         <v>493896</v>
       </c>
       <c r="R154" t="n">
-        <v>6834749</v>
+        <v>6834747</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16579,13 +16583,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316066</t>
+          <t>https://artportalen.se/Sighting/121316014</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121316126</v>
+        <v>121316066</v>
       </c>
       <c r="B155" t="n">
         <v>99118</v>
@@ -16620,10 +16624,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>493898</v>
+        <v>493896</v>
       </c>
       <c r="R155" t="n">
-        <v>6834798</v>
+        <v>6834749</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16681,13 +16685,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316126</t>
+          <t>https://artportalen.se/Sighting/121316066</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121316297</v>
+        <v>121316126</v>
       </c>
       <c r="B156" t="n">
         <v>99118</v>
@@ -16722,13 +16726,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>493886</v>
+        <v>493898</v>
       </c>
       <c r="R156" t="n">
-        <v>6834817</v>
+        <v>6834798</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16783,13 +16787,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316297</t>
+          <t>https://artportalen.se/Sighting/121316126</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121316463</v>
+        <v>121316297</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -16824,13 +16828,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>493838</v>
+        <v>493886</v>
       </c>
       <c r="R157" t="n">
-        <v>6834855</v>
+        <v>6834817</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16885,13 +16889,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316463</t>
+          <t>https://artportalen.se/Sighting/121316297</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121462959</v>
+        <v>121316463</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -16919,29 +16923,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>494001</v>
+        <v>493838</v>
       </c>
       <c r="R158" t="n">
-        <v>6834589</v>
+        <v>6834855</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16965,22 +16960,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16995,24 +16980,24 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121462959</t>
+          <t>https://artportalen.se/Sighting/121316463</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121463131</v>
+        <v>121462959</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -17042,30 +17027,27 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>494081</v>
+        <v>494001</v>
       </c>
       <c r="R159" t="n">
-        <v>6834614</v>
+        <v>6834589</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17094,7 +17076,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17104,7 +17086,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17113,31 +17095,30 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463131</t>
+          <t>https://artportalen.se/Sighting/121462959</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -17167,7 +17148,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -17184,10 +17165,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R160" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17219,7 +17200,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17229,7 +17210,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17256,13 +17237,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463365</t>
+          <t>https://artportalen.se/Sighting/121463131</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -17292,7 +17273,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -17309,10 +17290,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R161" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17344,7 +17325,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17354,7 +17335,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17381,13 +17362,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463743</t>
+          <t>https://artportalen.se/Sighting/121463365</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129456055</v>
+        <v>121463743</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -17417,24 +17398,27 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>493817</v>
+        <v>494116</v>
       </c>
       <c r="R162" t="n">
-        <v>6834930</v>
+        <v>6834573</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17461,12 +17445,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17475,30 +17469,31 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456055</t>
+          <t>https://artportalen.se/Sighting/121463743</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129456103</v>
+        <v>129456055</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -17528,7 +17523,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -17545,7 +17540,7 @@
         <v>493817</v>
       </c>
       <c r="R163" t="n">
-        <v>6834939</v>
+        <v>6834930</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17603,13 +17598,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456103</t>
+          <t>https://artportalen.se/Sighting/129456055</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129456176</v>
+        <v>129456103</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -17639,7 +17634,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -17653,10 +17648,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>493813</v>
+        <v>493817</v>
       </c>
       <c r="R164" t="n">
-        <v>6834955</v>
+        <v>6834939</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17714,13 +17709,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456176</t>
+          <t>https://artportalen.se/Sighting/129456103</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129456885</v>
+        <v>129456176</v>
       </c>
       <c r="B165" t="n">
         <v>99118</v>
@@ -17750,7 +17745,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -17764,10 +17759,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>493815</v>
+        <v>493813</v>
       </c>
       <c r="R165" t="n">
-        <v>6834917</v>
+        <v>6834955</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17825,13 +17820,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456885</t>
+          <t>https://artportalen.se/Sighting/129456176</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129514113</v>
+        <v>129456885</v>
       </c>
       <c r="B166" t="n">
         <v>99118</v>
@@ -17859,17 +17854,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>494256</v>
+        <v>493815</v>
       </c>
       <c r="R166" t="n">
-        <v>6834732</v>
+        <v>6834917</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17896,12 +17900,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17927,13 +17931,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129514113</t>
+          <t>https://artportalen.se/Sighting/129456885</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129520989</v>
+        <v>129514113</v>
       </c>
       <c r="B167" t="n">
         <v>99118</v>
@@ -17961,26 +17965,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>494262</v>
+        <v>494256</v>
       </c>
       <c r="R167" t="n">
-        <v>6834427</v>
+        <v>6834732</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18007,12 +18002,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18038,13 +18033,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520989</t>
+          <t>https://artportalen.se/Sighting/129514113</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129521085</v>
+        <v>129520989</v>
       </c>
       <c r="B168" t="n">
         <v>99118</v>
@@ -18072,17 +18067,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>494228</v>
+        <v>494262</v>
       </c>
       <c r="R168" t="n">
-        <v>6834405</v>
+        <v>6834427</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18140,13 +18144,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521085</t>
+          <t>https://artportalen.se/Sighting/129520989</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129521897</v>
+        <v>129521085</v>
       </c>
       <c r="B169" t="n">
         <v>99118</v>
@@ -18181,10 +18185,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>494323</v>
+        <v>494228</v>
       </c>
       <c r="R169" t="n">
-        <v>6834131</v>
+        <v>6834405</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18242,13 +18246,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521897</t>
+          <t>https://artportalen.se/Sighting/129521085</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129522294</v>
+        <v>129521897</v>
       </c>
       <c r="B170" t="n">
         <v>99118</v>
@@ -18283,10 +18287,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>494419</v>
+        <v>494323</v>
       </c>
       <c r="R170" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18344,13 +18348,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522294</t>
+          <t>https://artportalen.se/Sighting/129521897</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129522417</v>
+        <v>129522294</v>
       </c>
       <c r="B171" t="n">
         <v>99118</v>
@@ -18385,10 +18389,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>494442</v>
+        <v>494419</v>
       </c>
       <c r="R171" t="n">
-        <v>6834141</v>
+        <v>6834113</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18446,13 +18450,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522417</t>
+          <t>https://artportalen.se/Sighting/129522294</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129522632</v>
+        <v>129522417</v>
       </c>
       <c r="B172" t="n">
         <v>99118</v>
@@ -18480,26 +18484,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>494455</v>
+        <v>494442</v>
       </c>
       <c r="R172" t="n">
-        <v>6834185</v>
+        <v>6834141</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18557,13 +18552,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522632</t>
+          <t>https://artportalen.se/Sighting/129522417</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129522644</v>
+        <v>129522632</v>
       </c>
       <c r="B173" t="n">
         <v>99118</v>
@@ -18607,10 +18602,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>494450</v>
+        <v>494455</v>
       </c>
       <c r="R173" t="n">
-        <v>6834178</v>
+        <v>6834185</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18668,13 +18663,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522644</t>
+          <t>https://artportalen.se/Sighting/129522632</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129524059</v>
+        <v>129522644</v>
       </c>
       <c r="B174" t="n">
         <v>99118</v>
@@ -18704,7 +18699,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -18714,14 +18709,14 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>494582</v>
+        <v>494450</v>
       </c>
       <c r="R174" t="n">
-        <v>6834361</v>
+        <v>6834178</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18768,24 +18763,24 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524059</t>
+          <t>https://artportalen.se/Sighting/129522644</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129524619</v>
+        <v>129524059</v>
       </c>
       <c r="B175" t="n">
         <v>99118</v>
@@ -18815,7 +18810,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -18829,10 +18824,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>494338</v>
+        <v>494582</v>
       </c>
       <c r="R175" t="n">
-        <v>6834601</v>
+        <v>6834361</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18890,13 +18885,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524619</t>
+          <t>https://artportalen.se/Sighting/129524059</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129525359</v>
+        <v>129524619</v>
       </c>
       <c r="B176" t="n">
         <v>99118</v>
@@ -18926,7 +18921,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -18940,10 +18935,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>493934</v>
+        <v>494338</v>
       </c>
       <c r="R176" t="n">
-        <v>6834670</v>
+        <v>6834601</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19001,13 +18996,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129525359</t>
+          <t>https://artportalen.se/Sighting/129524619</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129525370</v>
+        <v>129525359</v>
       </c>
       <c r="B177" t="n">
         <v>99118</v>
@@ -19035,17 +19030,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>493942</v>
+        <v>493934</v>
       </c>
       <c r="R177" t="n">
-        <v>6834657</v>
+        <v>6834670</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19103,54 +19107,54 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129525370</t>
+          <t>https://artportalen.se/Sighting/129525359</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121464008</v>
+        <v>129525370</v>
       </c>
       <c r="B178" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>494068</v>
+        <v>493942</v>
       </c>
       <c r="R178" t="n">
-        <v>6834592</v>
+        <v>6834657</v>
       </c>
       <c r="S178" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19174,22 +19178,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19204,24 +19198,24 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121464008</t>
+          <t>https://artportalen.se/Sighting/129525370</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129511943</v>
+        <v>121464008</v>
       </c>
       <c r="B179" t="n">
         <v>79085</v>
@@ -19256,13 +19250,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>494635</v>
+        <v>494068</v>
       </c>
       <c r="R179" t="n">
-        <v>6834347</v>
+        <v>6834592</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19286,12 +19280,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19306,24 +19310,24 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511943</t>
+          <t>https://artportalen.se/Sighting/121464008</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129521425</v>
+        <v>129511943</v>
       </c>
       <c r="B180" t="n">
         <v>79085</v>
@@ -19354,14 +19358,14 @@
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>494187</v>
+        <v>494635</v>
       </c>
       <c r="R180" t="n">
-        <v>6834373</v>
+        <v>6834347</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19388,12 +19392,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19408,24 +19412,24 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521425</t>
+          <t>https://artportalen.se/Sighting/129511943</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129521475</v>
+        <v>129521425</v>
       </c>
       <c r="B181" t="n">
         <v>79085</v>
@@ -19456,14 +19460,14 @@
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>494181</v>
+        <v>494187</v>
       </c>
       <c r="R181" t="n">
-        <v>6834367</v>
+        <v>6834373</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19510,24 +19514,24 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521475</t>
+          <t>https://artportalen.se/Sighting/129521425</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129521663</v>
+        <v>129521475</v>
       </c>
       <c r="B182" t="n">
         <v>79085</v>
@@ -19558,14 +19562,14 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>494242</v>
+        <v>494181</v>
       </c>
       <c r="R182" t="n">
-        <v>6834295</v>
+        <v>6834367</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19612,24 +19616,24 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521663</t>
+          <t>https://artportalen.se/Sighting/129521475</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129522147</v>
+        <v>129521663</v>
       </c>
       <c r="B183" t="n">
         <v>79085</v>
@@ -19664,10 +19668,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>494385</v>
+        <v>494242</v>
       </c>
       <c r="R183" t="n">
-        <v>6834229</v>
+        <v>6834295</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19725,13 +19729,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522147</t>
+          <t>https://artportalen.se/Sighting/129521663</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129522256</v>
+        <v>129522147</v>
       </c>
       <c r="B184" t="n">
         <v>79085</v>
@@ -19766,10 +19770,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>494384</v>
+        <v>494385</v>
       </c>
       <c r="R184" t="n">
-        <v>6834211</v>
+        <v>6834229</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19827,13 +19831,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522256</t>
+          <t>https://artportalen.se/Sighting/129522147</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129522517</v>
+        <v>129522256</v>
       </c>
       <c r="B185" t="n">
         <v>79085</v>
@@ -19864,14 +19868,14 @@
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>494455</v>
+        <v>494384</v>
       </c>
       <c r="R185" t="n">
-        <v>6834176</v>
+        <v>6834211</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19918,24 +19922,24 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522517</t>
+          <t>https://artportalen.se/Sighting/129522256</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129523234</v>
+        <v>129522517</v>
       </c>
       <c r="B186" t="n">
         <v>79085</v>
@@ -19966,14 +19970,14 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>494472</v>
+        <v>494455</v>
       </c>
       <c r="R186" t="n">
-        <v>6834268</v>
+        <v>6834176</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20020,27 +20024,27 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523234</t>
+          <t>https://artportalen.se/Sighting/129522517</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129522138</v>
+        <v>129523234</v>
       </c>
       <c r="B187" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20048,21 +20052,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20072,13 +20076,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>494375</v>
+        <v>494472</v>
       </c>
       <c r="R187" t="n">
-        <v>6834215</v>
+        <v>6834268</v>
       </c>
       <c r="S187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20133,57 +20137,54 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522138</t>
+          <t>https://artportalen.se/Sighting/129523234</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>136488052</v>
+        <v>129522138</v>
       </c>
       <c r="B188" t="n">
-        <v>90884</v>
+        <v>79917</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>245044</v>
+        <v>229821</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>494214</v>
+        <v>494375</v>
       </c>
       <c r="R188" t="n">
-        <v>6834723</v>
+        <v>6834215</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20207,17 +20208,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Sex fruktkroppar i sandblotta invid myr.</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20226,56 +20222,55 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488052</t>
+          <t>https://artportalen.se/Sighting/129522138</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>136487945</v>
+        <v>136488052</v>
       </c>
       <c r="B189" t="n">
-        <v>93439</v>
+        <v>90884</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6332770</v>
+        <v>245044</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20288,7 +20283,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>494213</v>
+        <v>494214</v>
       </c>
       <c r="R189" t="n">
         <v>6834723</v>
@@ -20326,6 +20321,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Sex fruktkroppar i sandblotta invid myr.</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -20349,6 +20349,112 @@
       </c>
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136488052</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>136487945</v>
+      </c>
+      <c r="B190" t="n">
+        <v>93439</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Korplamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>494213</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6834723</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136487945</t>
         </is>
@@ -20544,6 +20650,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136934641</v>
       </c>
       <c r="B42" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136487855</v>
       </c>
       <c r="B52" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488085</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488093</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488195</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488215</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>136488233</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>136488247</v>
       </c>
       <c r="B120" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>136488262</v>
       </c>
       <c r="B121" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>136488052</v>
       </c>
       <c r="B189" t="n">
-        <v>90884</v>
+        <v>90886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136487945</v>
       </c>
       <c r="B190" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -4693,7 +4693,7 @@
         <v>136488016</v>
       </c>
       <c r="B40" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>136488256</v>
       </c>
       <c r="B41" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136934641</v>
       </c>
       <c r="B42" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>136487855</v>
       </c>
       <c r="B52" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>136488085</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>136488093</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>136488195</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>136488215</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>136488233</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>136488247</v>
       </c>
       <c r="B120" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>136488262</v>
       </c>
       <c r="B121" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>136488052</v>
       </c>
       <c r="B189" t="n">
-        <v>90886</v>
+        <v>90888</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>136487945</v>
       </c>
       <c r="B190" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136488016</v>
       </c>
       <c r="B58" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136488256</v>
       </c>
       <c r="B59" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>136487855</v>
       </c>
       <c r="B74" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>136488085</v>
       </c>
       <c r="B75" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>136488093</v>
       </c>
       <c r="B76" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136488195</v>
       </c>
       <c r="B77" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>136488215</v>
       </c>
       <c r="B78" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136488233</v>
       </c>
       <c r="B79" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
@@ -27775,7 +27775,7 @@
         <v>136487945</v>
       </c>
       <c r="B261" t="n">
-        <v>93444</v>
+        <v>93450</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>136488016</v>
       </c>
       <c r="B58" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>136488256</v>
       </c>
       <c r="B59" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>136487855</v>
       </c>
       <c r="B74" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>136488085</v>
       </c>
       <c r="B75" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>136488093</v>
       </c>
       <c r="B76" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>136488195</v>
       </c>
       <c r="B77" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>136488215</v>
       </c>
       <c r="B78" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>136488233</v>
       </c>
       <c r="B79" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>136488247</v>
       </c>
       <c r="B163" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136488262</v>
       </c>
       <c r="B164" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90895</v>
+        <v>90899</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>136487945</v>
       </c>
       <c r="B261" t="n">
-        <v>93450</v>
+        <v>93454</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90899</v>
+        <v>90901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>137097713</v>
       </c>
       <c r="B213" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>137095389</v>
       </c>
       <c r="B217" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90901</v>
+        <v>90914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>137097713</v>
       </c>
       <c r="B213" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>137095389</v>
       </c>
       <c r="B217" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90914</v>
+        <v>90916</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -9112,11 +9112,7 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Dlr</t>
@@ -9450,11 +9446,7 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Korplamm, Dlr</t>
@@ -10117,11 +10109,7 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Korplamm, Dlr</t>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90916</v>
+        <v>90919</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>137097713</v>
       </c>
       <c r="B213" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>137095389</v>
       </c>
       <c r="B217" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90919</v>
+        <v>90929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90929</v>
+        <v>90930</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>137097713</v>
       </c>
       <c r="B213" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>137095389</v>
       </c>
       <c r="B217" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90930</v>
+        <v>90933</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90933</v>
+        <v>90935</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90756</v>
+        <v>90761</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>137097713</v>
       </c>
       <c r="B213" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>137095389</v>
       </c>
       <c r="B217" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90935</v>
+        <v>90940</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90761</v>
+        <v>90772</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90940</v>
+        <v>90951</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90772</v>
+        <v>90773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90951</v>
+        <v>90952</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90773</v>
+        <v>90776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>137094009</v>
       </c>
       <c r="B100" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137094149</v>
       </c>
       <c r="B101" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>137095229</v>
       </c>
       <c r="B102" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>137096333</v>
       </c>
       <c r="B103" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>137093981</v>
       </c>
       <c r="B165" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>137093998</v>
       </c>
       <c r="B166" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>137094113</v>
       </c>
       <c r="B167" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>137094135</v>
       </c>
       <c r="B168" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>137094239</v>
       </c>
       <c r="B169" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>137094252</v>
       </c>
       <c r="B170" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>137094267</v>
       </c>
       <c r="B171" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>137095160</v>
       </c>
       <c r="B172" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>137095527</v>
       </c>
       <c r="B173" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>137095880</v>
       </c>
       <c r="B174" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>137096177</v>
       </c>
       <c r="B175" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>137096195</v>
       </c>
       <c r="B176" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137096277</v>
       </c>
       <c r="B177" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>137096359</v>
       </c>
       <c r="B178" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>137098622</v>
       </c>
       <c r="B179" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>137098678</v>
       </c>
       <c r="B180" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>137094222</v>
       </c>
       <c r="B186" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>137094663</v>
       </c>
       <c r="B187" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>137093799</v>
       </c>
       <c r="B188" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>137094121</v>
       </c>
       <c r="B189" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>137097767</v>
       </c>
       <c r="B190" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>137098648</v>
       </c>
       <c r="B191" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>137095442</v>
       </c>
       <c r="B206" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>137098828</v>
       </c>
       <c r="B207" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>137097763</v>
       </c>
       <c r="B257" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>137098795</v>
       </c>
       <c r="B258" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>136488052</v>
       </c>
       <c r="B260" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93501</v>
+        <v>93502</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ261"/>
+  <dimension ref="A1:AZ262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3979,7 +3979,7 @@
         <v>137093860</v>
       </c>
       <c r="B33" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>137093864</v>
       </c>
       <c r="B34" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>137093910</v>
       </c>
       <c r="B35" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>137093967</v>
       </c>
       <c r="B36" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>137093995</v>
       </c>
       <c r="B37" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>137094099</v>
       </c>
       <c r="B38" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137094261</v>
       </c>
       <c r="B39" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>137094661</v>
       </c>
       <c r="B40" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137094678</v>
       </c>
       <c r="B41" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>137094713</v>
       </c>
       <c r="B42" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>137095799</v>
       </c>
       <c r="B43" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>137095888</v>
       </c>
       <c r="B44" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>137096360</v>
       </c>
       <c r="B45" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137096670</v>
       </c>
       <c r="B46" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>137097439</v>
       </c>
       <c r="B53" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>137093830</v>
       </c>
       <c r="B55" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>137093982</v>
       </c>
       <c r="B56" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>137098766</v>
       </c>
       <c r="B57" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136934641</v>
       </c>
       <c r="B60" t="n">
-        <v>93502</v>
+        <v>93505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>137093845</v>
       </c>
       <c r="B61" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>137097657</v>
       </c>
       <c r="B62" t="n">
-        <v>93501</v>
+        <v>93505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>137098959</v>
       </c>
       <c r="B70" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>137097860</v>
       </c>
       <c r="B71" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>137093868</v>
       </c>
       <c r="B80" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>137094344</v>
       </c>
       <c r="B81" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137095348</v>
       </c>
       <c r="B82" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>137097307</v>
       </c>
       <c r="B83" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137097321</v>
       </c>
       <c r="B84" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>137097353</v>
       </c>
       <c r="B85" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>137097715</v>
       </c>
       <c r="B86" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>137097756</v>
       </c>
       <c r="B87" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>137097766</v>
       </c>
       <c r="B88" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137098215</v>
       </c>
       <c r="B89" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>137098256</v>
       </c>
       <c r="B90" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>137098606</v>
       </c>
       <c r="B91" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137098763</v>
       </c>
       <c r="B92" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137098970</v>
       </c>
       <c r="B93" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137099447</v>
       </c>
       <c r="B94" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137099137</v>
       </c>
       <c r="B95" t="n">
-        <v>90776</v>
+        <v>90780</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>137094312</v>
       </c>
       <c r="B98" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11036,48 +11036,51 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137094009</v>
+        <v>137552510</v>
       </c>
       <c r="B100" t="n">
-        <v>93469</v>
+        <v>93515</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6055</v>
+        <v>5448</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494777</v>
+        <v>494719</v>
       </c>
       <c r="R100" t="n">
-        <v>6834152</v>
+        <v>6834109</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11101,12 +11104,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11115,33 +11118,34 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094009</t>
+          <t>https://artportalen.se/Sighting/137552510</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137094149</v>
+        <v>137094009</v>
       </c>
       <c r="B101" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11173,10 +11177,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494735</v>
+        <v>494777</v>
       </c>
       <c r="R101" t="n">
-        <v>6834210</v>
+        <v>6834152</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11234,16 +11238,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094149</t>
+          <t>https://artportalen.se/Sighting/137094009</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137095229</v>
+        <v>137094149</v>
       </c>
       <c r="B102" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11275,10 +11279,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494708</v>
+        <v>494735</v>
       </c>
       <c r="R102" t="n">
-        <v>6834356</v>
+        <v>6834210</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11336,16 +11340,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095229</t>
+          <t>https://artportalen.se/Sighting/137094149</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137096333</v>
+        <v>137095229</v>
       </c>
       <c r="B103" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11377,10 +11381,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494479</v>
+        <v>494708</v>
       </c>
       <c r="R103" t="n">
-        <v>6833932</v>
+        <v>6834356</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11438,16 +11442,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137096333</t>
+          <t>https://artportalen.se/Sighting/137095229</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121313238</v>
+        <v>137096333</v>
       </c>
       <c r="B104" t="n">
-        <v>79327</v>
+        <v>93473</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11455,37 +11459,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6055</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493815</v>
+        <v>494479</v>
       </c>
       <c r="R104" t="n">
-        <v>6834929</v>
+        <v>6833932</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11509,12 +11513,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11529,24 +11533,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313238</t>
+          <t>https://artportalen.se/Sighting/137096333</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121462834</v>
+        <v>121313238</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11577,17 +11581,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494009</v>
+        <v>493815</v>
       </c>
       <c r="R105" t="n">
-        <v>6834570</v>
+        <v>6834929</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11611,27 +11615,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11646,24 +11635,24 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121462834</t>
+          <t>https://artportalen.se/Sighting/121313238</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121463067</v>
+        <v>121462834</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11698,10 +11687,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493995</v>
+        <v>494009</v>
       </c>
       <c r="R106" t="n">
-        <v>6834619</v>
+        <v>6834570</v>
       </c>
       <c r="S106" t="n">
         <v>9</v>
@@ -11733,7 +11722,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11743,12 +11732,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Gran och tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11774,13 +11763,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463067</t>
+          <t>https://artportalen.se/Sighting/121462834</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121463429</v>
+        <v>121463067</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -11815,10 +11804,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494075</v>
+        <v>493995</v>
       </c>
       <c r="R107" t="n">
-        <v>6834606</v>
+        <v>6834619</v>
       </c>
       <c r="S107" t="n">
         <v>9</v>
@@ -11850,7 +11839,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11860,12 +11849,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Gran och tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11891,13 +11880,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463429</t>
+          <t>https://artportalen.se/Sighting/121463067</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121463770</v>
+        <v>121463429</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -11932,10 +11921,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494125</v>
+        <v>494075</v>
       </c>
       <c r="R108" t="n">
-        <v>6834588</v>
+        <v>6834606</v>
       </c>
       <c r="S108" t="n">
         <v>9</v>
@@ -11967,7 +11956,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11977,12 +11966,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12002,19 +11991,19 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anders Heggestad, Lisa Olson, Lars-Erik Nilsson, Göran Ehn</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463770</t>
+          <t>https://artportalen.se/Sighting/121463429</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129511911</v>
+        <v>121463770</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12049,13 +12038,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494614</v>
+        <v>494125</v>
       </c>
       <c r="R109" t="n">
-        <v>6834378</v>
+        <v>6834588</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12079,12 +12068,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12099,24 +12103,24 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bo karlstens, Anders Heggestad, Lisa Olson, Lars-Erik Nilsson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511911</t>
+          <t>https://artportalen.se/Sighting/121463770</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129511957</v>
+        <v>129511911</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12151,10 +12155,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494635</v>
+        <v>494614</v>
       </c>
       <c r="R110" t="n">
-        <v>6834347</v>
+        <v>6834378</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12212,13 +12216,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511957</t>
+          <t>https://artportalen.se/Sighting/129511911</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129511985</v>
+        <v>129511957</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12253,10 +12257,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494672</v>
+        <v>494635</v>
       </c>
       <c r="R111" t="n">
-        <v>6834352</v>
+        <v>6834347</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12314,13 +12318,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511985</t>
+          <t>https://artportalen.se/Sighting/129511957</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129512105</v>
+        <v>129511985</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12355,10 +12359,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494664</v>
+        <v>494672</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834352</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12416,13 +12420,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512105</t>
+          <t>https://artportalen.se/Sighting/129511985</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129512125</v>
+        <v>129512105</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12457,10 +12461,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494678</v>
+        <v>494664</v>
       </c>
       <c r="R113" t="n">
-        <v>6834243</v>
+        <v>6834295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12518,13 +12522,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512125</t>
+          <t>https://artportalen.se/Sighting/129512105</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129512195</v>
+        <v>129512125</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12559,10 +12563,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494612</v>
+        <v>494678</v>
       </c>
       <c r="R114" t="n">
-        <v>6834233</v>
+        <v>6834243</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12620,13 +12624,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512195</t>
+          <t>https://artportalen.se/Sighting/129512125</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129512298</v>
+        <v>129512195</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12661,10 +12665,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494611</v>
+        <v>494612</v>
       </c>
       <c r="R115" t="n">
-        <v>6834107</v>
+        <v>6834233</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12722,13 +12726,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512298</t>
+          <t>https://artportalen.se/Sighting/129512195</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129512361</v>
+        <v>129512298</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -12763,10 +12767,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494634</v>
+        <v>494611</v>
       </c>
       <c r="R116" t="n">
-        <v>6834067</v>
+        <v>6834107</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12824,13 +12828,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512361</t>
+          <t>https://artportalen.se/Sighting/129512298</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129512658</v>
+        <v>129512361</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -12865,10 +12869,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494506</v>
+        <v>494634</v>
       </c>
       <c r="R117" t="n">
-        <v>6834042</v>
+        <v>6834067</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12926,13 +12930,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512658</t>
+          <t>https://artportalen.se/Sighting/129512361</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129512676</v>
+        <v>129512658</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -12967,10 +12971,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494500</v>
+        <v>494506</v>
       </c>
       <c r="R118" t="n">
-        <v>6834016</v>
+        <v>6834042</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13028,13 +13032,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512676</t>
+          <t>https://artportalen.se/Sighting/129512658</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129512771</v>
+        <v>129512676</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13069,10 +13073,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494466</v>
+        <v>494500</v>
       </c>
       <c r="R119" t="n">
-        <v>6833989</v>
+        <v>6834016</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13130,13 +13134,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512771</t>
+          <t>https://artportalen.se/Sighting/129512676</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129512788</v>
+        <v>129512771</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13171,10 +13175,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494465</v>
+        <v>494466</v>
       </c>
       <c r="R120" t="n">
-        <v>6833963</v>
+        <v>6833989</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13232,13 +13236,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512788</t>
+          <t>https://artportalen.se/Sighting/129512771</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129512918</v>
+        <v>129512788</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13273,10 +13277,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494417</v>
+        <v>494465</v>
       </c>
       <c r="R121" t="n">
-        <v>6833948</v>
+        <v>6833963</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13334,13 +13338,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512918</t>
+          <t>https://artportalen.se/Sighting/129512788</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129513122</v>
+        <v>129512918</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13375,10 +13379,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494490</v>
+        <v>494417</v>
       </c>
       <c r="R122" t="n">
-        <v>6834127</v>
+        <v>6833948</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13436,13 +13440,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513122</t>
+          <t>https://artportalen.se/Sighting/129512918</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129513342</v>
+        <v>129513122</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13477,10 +13481,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494384</v>
+        <v>494490</v>
       </c>
       <c r="R123" t="n">
-        <v>6834354</v>
+        <v>6834127</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13538,13 +13542,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513342</t>
+          <t>https://artportalen.se/Sighting/129513122</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129513370</v>
+        <v>129513342</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13579,10 +13583,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494369</v>
+        <v>494384</v>
       </c>
       <c r="R124" t="n">
-        <v>6834380</v>
+        <v>6834354</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13640,13 +13644,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513370</t>
+          <t>https://artportalen.se/Sighting/129513342</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129513412</v>
+        <v>129513370</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -13681,10 +13685,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494427</v>
+        <v>494369</v>
       </c>
       <c r="R125" t="n">
-        <v>6834434</v>
+        <v>6834380</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13742,13 +13746,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513412</t>
+          <t>https://artportalen.se/Sighting/129513370</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129513741</v>
+        <v>129513412</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -13783,10 +13787,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494548</v>
+        <v>494427</v>
       </c>
       <c r="R126" t="n">
-        <v>6834603</v>
+        <v>6834434</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13844,13 +13848,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513741</t>
+          <t>https://artportalen.se/Sighting/129513412</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129513963</v>
+        <v>129513741</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -13881,14 +13885,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494311</v>
+        <v>494548</v>
       </c>
       <c r="R127" t="n">
-        <v>6834701</v>
+        <v>6834603</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13946,13 +13950,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129513963</t>
+          <t>https://artportalen.se/Sighting/129513741</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129520902</v>
+        <v>129513963</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -13983,14 +13987,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494278</v>
+        <v>494311</v>
       </c>
       <c r="R128" t="n">
-        <v>6834456</v>
+        <v>6834701</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14017,12 +14021,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14037,24 +14041,24 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520902</t>
+          <t>https://artportalen.se/Sighting/129513963</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129520912</v>
+        <v>129520902</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14085,14 +14089,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494290</v>
+        <v>494278</v>
       </c>
       <c r="R129" t="n">
-        <v>6834454</v>
+        <v>6834456</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14139,24 +14143,24 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520912</t>
+          <t>https://artportalen.se/Sighting/129520902</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129520952</v>
+        <v>129520912</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14191,7 +14195,7 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494291</v>
+        <v>494290</v>
       </c>
       <c r="R130" t="n">
         <v>6834454</v>
@@ -14252,13 +14256,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520952</t>
+          <t>https://artportalen.se/Sighting/129520912</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129521002</v>
+        <v>129520952</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14289,14 +14293,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494241</v>
+        <v>494291</v>
       </c>
       <c r="R131" t="n">
-        <v>6834425</v>
+        <v>6834454</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14343,24 +14347,24 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521002</t>
+          <t>https://artportalen.se/Sighting/129520952</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521072</v>
+        <v>129521002</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14395,10 +14399,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494234</v>
+        <v>494241</v>
       </c>
       <c r="R132" t="n">
-        <v>6834416</v>
+        <v>6834425</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14456,13 +14460,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521072</t>
+          <t>https://artportalen.se/Sighting/129521002</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521144</v>
+        <v>129521072</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14497,10 +14501,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494222</v>
+        <v>494234</v>
       </c>
       <c r="R133" t="n">
-        <v>6834390</v>
+        <v>6834416</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14558,13 +14562,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521144</t>
+          <t>https://artportalen.se/Sighting/129521072</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521147</v>
+        <v>129521144</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -14595,14 +14599,14 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494225</v>
+        <v>494222</v>
       </c>
       <c r="R134" t="n">
-        <v>6834382</v>
+        <v>6834390</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14649,24 +14653,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521147</t>
+          <t>https://artportalen.se/Sighting/129521144</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521302</v>
+        <v>129521147</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -14697,17 +14701,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494215</v>
+        <v>494225</v>
       </c>
       <c r="R135" t="n">
-        <v>6834362</v>
+        <v>6834382</v>
       </c>
       <c r="S135" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14751,24 +14755,24 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521302</t>
+          <t>https://artportalen.se/Sighting/129521147</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129521418</v>
+        <v>129521302</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -14799,17 +14803,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494176</v>
+        <v>494215</v>
       </c>
       <c r="R136" t="n">
-        <v>6834368</v>
+        <v>6834362</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14853,24 +14857,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521418</t>
+          <t>https://artportalen.se/Sighting/129521302</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129521804</v>
+        <v>129521418</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -14901,17 +14905,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494297</v>
+        <v>494176</v>
       </c>
       <c r="R137" t="n">
-        <v>6834314</v>
+        <v>6834368</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14955,24 +14959,24 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521804</t>
+          <t>https://artportalen.se/Sighting/129521418</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129521823</v>
+        <v>129521804</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15003,17 +15007,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494360</v>
+        <v>494297</v>
       </c>
       <c r="R138" t="n">
-        <v>6834206</v>
+        <v>6834314</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15057,24 +15061,24 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521823</t>
+          <t>https://artportalen.se/Sighting/129521804</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129521967</v>
+        <v>129521823</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15105,17 +15109,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>494346</v>
+        <v>494360</v>
       </c>
       <c r="R139" t="n">
-        <v>6834277</v>
+        <v>6834206</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15159,24 +15163,24 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521967</t>
+          <t>https://artportalen.se/Sighting/129521823</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129522129</v>
+        <v>129521967</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15207,14 +15211,14 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>494397</v>
+        <v>494346</v>
       </c>
       <c r="R140" t="n">
-        <v>6834116</v>
+        <v>6834277</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15261,24 +15265,24 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522129</t>
+          <t>https://artportalen.se/Sighting/129521967</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129522450</v>
+        <v>129522129</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15309,17 +15313,17 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>494325</v>
+        <v>494397</v>
       </c>
       <c r="R141" t="n">
-        <v>6834177</v>
+        <v>6834116</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15363,24 +15367,24 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522450</t>
+          <t>https://artportalen.se/Sighting/129522129</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15411,17 +15415,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R142" t="n">
         <v>6834177</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15465,24 +15469,24 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522454</t>
+          <t>https://artportalen.se/Sighting/129522450</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129522706</v>
+        <v>129522454</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -15513,17 +15517,17 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>494454</v>
+        <v>494456</v>
       </c>
       <c r="R143" t="n">
-        <v>6834225</v>
+        <v>6834177</v>
       </c>
       <c r="S143" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15567,24 +15571,24 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522706</t>
+          <t>https://artportalen.se/Sighting/129522454</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129522819</v>
+        <v>129522706</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -15619,13 +15623,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>494470</v>
+        <v>494454</v>
       </c>
       <c r="R144" t="n">
-        <v>6834231</v>
+        <v>6834225</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15680,13 +15684,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522819</t>
+          <t>https://artportalen.se/Sighting/129522706</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129522857</v>
+        <v>129522819</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -15721,10 +15725,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>494475</v>
+        <v>494470</v>
       </c>
       <c r="R145" t="n">
-        <v>6834232</v>
+        <v>6834231</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15782,13 +15786,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522857</t>
+          <t>https://artportalen.se/Sighting/129522819</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129522903</v>
+        <v>129522857</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -15823,10 +15827,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>494466</v>
+        <v>494475</v>
       </c>
       <c r="R146" t="n">
-        <v>6834211</v>
+        <v>6834232</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15884,13 +15888,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522903</t>
+          <t>https://artportalen.se/Sighting/129522857</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129523005</v>
+        <v>129522903</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -15925,10 +15929,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>494491</v>
+        <v>494466</v>
       </c>
       <c r="R147" t="n">
-        <v>6834229</v>
+        <v>6834211</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15986,13 +15990,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523005</t>
+          <t>https://artportalen.se/Sighting/129522903</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129523011</v>
+        <v>129523005</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16023,14 +16027,14 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>494480</v>
+        <v>494491</v>
       </c>
       <c r="R148" t="n">
-        <v>6834232</v>
+        <v>6834229</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16077,24 +16081,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523011</t>
+          <t>https://artportalen.se/Sighting/129523005</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129524130</v>
+        <v>129523011</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16129,10 +16133,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>494537</v>
+        <v>494480</v>
       </c>
       <c r="R149" t="n">
-        <v>6834492</v>
+        <v>6834232</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16190,13 +16194,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524130</t>
+          <t>https://artportalen.se/Sighting/129523011</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129524189</v>
+        <v>129524130</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16227,17 +16231,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>494606</v>
+        <v>494537</v>
       </c>
       <c r="R150" t="n">
-        <v>6834497</v>
+        <v>6834492</v>
       </c>
       <c r="S150" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16281,24 +16285,24 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524189</t>
+          <t>https://artportalen.se/Sighting/129524130</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129524246</v>
+        <v>129524189</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16333,13 +16337,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>494560</v>
+        <v>494606</v>
       </c>
       <c r="R151" t="n">
-        <v>6834565</v>
+        <v>6834497</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16394,13 +16398,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524246</t>
+          <t>https://artportalen.se/Sighting/129524189</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129524342</v>
+        <v>129524246</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -16435,13 +16439,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>494544</v>
+        <v>494560</v>
       </c>
       <c r="R152" t="n">
-        <v>6834616</v>
+        <v>6834565</v>
       </c>
       <c r="S152" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16496,13 +16500,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524342</t>
+          <t>https://artportalen.se/Sighting/129524246</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129524381</v>
+        <v>129524342</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -16533,17 +16537,17 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>494485</v>
+        <v>494544</v>
       </c>
       <c r="R153" t="n">
-        <v>6834612</v>
+        <v>6834616</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16587,24 +16591,24 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524381</t>
+          <t>https://artportalen.se/Sighting/129524342</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129524385</v>
+        <v>129524381</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -16635,17 +16639,17 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>494528</v>
+        <v>494485</v>
       </c>
       <c r="R154" t="n">
-        <v>6834660</v>
+        <v>6834612</v>
       </c>
       <c r="S154" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16689,24 +16693,24 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524385</t>
+          <t>https://artportalen.se/Sighting/129524381</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129524525</v>
+        <v>129524385</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -16737,17 +16741,17 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>494354</v>
+        <v>494528</v>
       </c>
       <c r="R155" t="n">
-        <v>6834662</v>
+        <v>6834660</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16791,24 +16795,24 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524525</t>
+          <t>https://artportalen.se/Sighting/129524385</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129524530</v>
+        <v>129524525</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -16839,14 +16843,14 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>494349</v>
+        <v>494354</v>
       </c>
       <c r="R156" t="n">
-        <v>6834653</v>
+        <v>6834662</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16893,24 +16897,24 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524530</t>
+          <t>https://artportalen.se/Sighting/129524525</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129524747</v>
+        <v>129524530</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -16941,14 +16945,14 @@
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>494401</v>
+        <v>494349</v>
       </c>
       <c r="R157" t="n">
-        <v>6834640</v>
+        <v>6834653</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16995,24 +16999,24 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524747</t>
+          <t>https://artportalen.se/Sighting/129524530</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129524762</v>
+        <v>129524747</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17043,14 +17047,14 @@
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>494406</v>
+        <v>494401</v>
       </c>
       <c r="R158" t="n">
-        <v>6834477</v>
+        <v>6834640</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17097,24 +17101,24 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524762</t>
+          <t>https://artportalen.se/Sighting/129524747</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129524775</v>
+        <v>129524762</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17149,10 +17153,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>494416</v>
+        <v>494406</v>
       </c>
       <c r="R159" t="n">
-        <v>6834464</v>
+        <v>6834477</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17210,13 +17214,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524775</t>
+          <t>https://artportalen.se/Sighting/129524762</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129524779</v>
+        <v>129524775</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17251,10 +17255,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>494423</v>
+        <v>494416</v>
       </c>
       <c r="R160" t="n">
-        <v>6834463</v>
+        <v>6834464</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17312,13 +17316,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524779</t>
+          <t>https://artportalen.se/Sighting/129524775</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129524785</v>
+        <v>129524779</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -17353,10 +17357,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>494405</v>
+        <v>494423</v>
       </c>
       <c r="R161" t="n">
-        <v>6834446</v>
+        <v>6834463</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17414,13 +17418,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524785</t>
+          <t>https://artportalen.se/Sighting/129524779</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129524791</v>
+        <v>129524785</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -17455,10 +17459,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>494381</v>
+        <v>494405</v>
       </c>
       <c r="R162" t="n">
-        <v>6834429</v>
+        <v>6834446</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17516,16 +17520,16 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524791</t>
+          <t>https://artportalen.se/Sighting/129524785</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>136488247</v>
+        <v>129524791</v>
       </c>
       <c r="B163" t="n">
-        <v>79485</v>
+        <v>79327</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17551,19 +17555,16 @@
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>494507</v>
+        <v>494381</v>
       </c>
       <c r="R163" t="n">
-        <v>6833914</v>
+        <v>6834429</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17590,12 +17591,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17604,31 +17605,30 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488247</t>
+          <t>https://artportalen.se/Sighting/129524791</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>136488262</v>
+        <v>136488247</v>
       </c>
       <c r="B164" t="n">
         <v>79485</v>
@@ -17666,10 +17666,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>494332</v>
+        <v>494507</v>
       </c>
       <c r="R164" t="n">
-        <v>6834191</v>
+        <v>6833914</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17728,16 +17728,16 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488262</t>
+          <t>https://artportalen.se/Sighting/136488247</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>137093981</v>
+        <v>136488262</v>
       </c>
       <c r="B165" t="n">
-        <v>79535</v>
+        <v>79485</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17763,19 +17763,22 @@
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>494655</v>
+        <v>494332</v>
       </c>
       <c r="R165" t="n">
-        <v>6834286</v>
+        <v>6834191</v>
       </c>
       <c r="S165" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17799,12 +17802,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17813,33 +17816,34 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093981</t>
+          <t>https://artportalen.se/Sighting/136488262</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>137093998</v>
+        <v>137093981</v>
       </c>
       <c r="B166" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17871,13 +17875,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>494648</v>
+        <v>494655</v>
       </c>
       <c r="R166" t="n">
-        <v>6834255</v>
+        <v>6834286</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17932,16 +17936,16 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093998</t>
+          <t>https://artportalen.se/Sighting/137093981</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>137094113</v>
+        <v>137093998</v>
       </c>
       <c r="B167" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17973,13 +17977,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>494761</v>
+        <v>494648</v>
       </c>
       <c r="R167" t="n">
-        <v>6834150</v>
+        <v>6834255</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18023,27 +18027,27 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094113</t>
+          <t>https://artportalen.se/Sighting/137093998</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>137094135</v>
+        <v>137094113</v>
       </c>
       <c r="B168" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18075,10 +18079,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>494743</v>
+        <v>494761</v>
       </c>
       <c r="R168" t="n">
-        <v>6834205</v>
+        <v>6834150</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -18136,16 +18140,16 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094135</t>
+          <t>https://artportalen.se/Sighting/137094113</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>137094239</v>
+        <v>137094135</v>
       </c>
       <c r="B169" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18177,13 +18181,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>494659</v>
+        <v>494743</v>
       </c>
       <c r="R169" t="n">
-        <v>6834180</v>
+        <v>6834205</v>
       </c>
       <c r="S169" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -18227,27 +18231,27 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094239</t>
+          <t>https://artportalen.se/Sighting/137094135</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>137094252</v>
+        <v>137094239</v>
       </c>
       <c r="B170" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18279,13 +18283,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>494715</v>
+        <v>494659</v>
       </c>
       <c r="R170" t="n">
-        <v>6834142</v>
+        <v>6834180</v>
       </c>
       <c r="S170" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18329,27 +18333,27 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094252</t>
+          <t>https://artportalen.se/Sighting/137094239</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>137094267</v>
+        <v>137094252</v>
       </c>
       <c r="B171" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18381,13 +18385,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>494636</v>
+        <v>494715</v>
       </c>
       <c r="R171" t="n">
-        <v>6834170</v>
+        <v>6834142</v>
       </c>
       <c r="S171" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18431,27 +18435,27 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094267</t>
+          <t>https://artportalen.se/Sighting/137094252</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>137095160</v>
+        <v>137094267</v>
       </c>
       <c r="B172" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18483,10 +18487,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>494673</v>
+        <v>494636</v>
       </c>
       <c r="R172" t="n">
-        <v>6834352</v>
+        <v>6834170</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -18544,16 +18548,16 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095160</t>
+          <t>https://artportalen.se/Sighting/137094267</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>137095527</v>
+        <v>137095160</v>
       </c>
       <c r="B173" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18585,13 +18589,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>494599</v>
+        <v>494673</v>
       </c>
       <c r="R173" t="n">
-        <v>6834186</v>
+        <v>6834352</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18635,27 +18639,27 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095527</t>
+          <t>https://artportalen.se/Sighting/137095160</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>137095880</v>
+        <v>137095527</v>
       </c>
       <c r="B174" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18687,10 +18691,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>494568</v>
+        <v>494599</v>
       </c>
       <c r="R174" t="n">
-        <v>6834017</v>
+        <v>6834186</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -18748,16 +18752,16 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095880</t>
+          <t>https://artportalen.se/Sighting/137095527</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>137096177</v>
+        <v>137095880</v>
       </c>
       <c r="B175" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18789,10 +18793,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>494542</v>
+        <v>494568</v>
       </c>
       <c r="R175" t="n">
-        <v>6833975</v>
+        <v>6834017</v>
       </c>
       <c r="S175" t="n">
         <v>5</v>
@@ -18850,16 +18854,16 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137096177</t>
+          <t>https://artportalen.se/Sighting/137095880</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>137096195</v>
+        <v>137096177</v>
       </c>
       <c r="B176" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18891,13 +18895,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>494506</v>
+        <v>494542</v>
       </c>
       <c r="R176" t="n">
-        <v>6834007</v>
+        <v>6833975</v>
       </c>
       <c r="S176" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18941,27 +18945,27 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137096195</t>
+          <t>https://artportalen.se/Sighting/137096177</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>137096277</v>
+        <v>137096195</v>
       </c>
       <c r="B177" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18993,10 +18997,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>494490</v>
+        <v>494506</v>
       </c>
       <c r="R177" t="n">
-        <v>6833952</v>
+        <v>6834007</v>
       </c>
       <c r="S177" t="n">
         <v>20</v>
@@ -19054,16 +19058,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137096277</t>
+          <t>https://artportalen.se/Sighting/137096195</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>137096359</v>
+        <v>137096277</v>
       </c>
       <c r="B178" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19095,13 +19099,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>494471</v>
+        <v>494490</v>
       </c>
       <c r="R178" t="n">
-        <v>6833924</v>
+        <v>6833952</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -19145,27 +19149,27 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137096359</t>
+          <t>https://artportalen.se/Sighting/137096277</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>137098622</v>
+        <v>137096359</v>
       </c>
       <c r="B179" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19197,10 +19201,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>494588</v>
+        <v>494471</v>
       </c>
       <c r="R179" t="n">
-        <v>6834553</v>
+        <v>6833924</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19258,16 +19262,16 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137098622</t>
+          <t>https://artportalen.se/Sighting/137096359</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>137098678</v>
+        <v>137098622</v>
       </c>
       <c r="B180" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19299,10 +19303,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>494609</v>
+        <v>494588</v>
       </c>
       <c r="R180" t="n">
-        <v>6834510</v>
+        <v>6834553</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -19360,57 +19364,54 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137098678</t>
+          <t>https://artportalen.se/Sighting/137098622</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>134851616</v>
+        <v>137098678</v>
       </c>
       <c r="B181" t="n">
-        <v>79500</v>
+        <v>79539</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>494545</v>
+        <v>494609</v>
       </c>
       <c r="R181" t="n">
-        <v>6834524</v>
+        <v>6834510</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19434,12 +19435,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19448,72 +19449,74 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134851616</t>
+          <t>https://artportalen.se/Sighting/137098678</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121463076</v>
+        <v>134851616</v>
       </c>
       <c r="B182" t="n">
-        <v>83307</v>
+        <v>79500</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>494009</v>
+        <v>494545</v>
       </c>
       <c r="R182" t="n">
-        <v>6834588</v>
+        <v>6834524</v>
       </c>
       <c r="S182" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19537,22 +19540,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19561,33 +19554,34 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463076</t>
+          <t>https://artportalen.se/Sighting/134851616</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129520975</v>
+        <v>121463076</v>
       </c>
       <c r="B183" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19595,34 +19589,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>494243</v>
+        <v>494009</v>
       </c>
       <c r="R183" t="n">
-        <v>6834445</v>
+        <v>6834588</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -19649,12 +19643,22 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19669,24 +19673,24 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520975</t>
+          <t>https://artportalen.se/Sighting/121463076</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129522151</v>
+        <v>129520975</v>
       </c>
       <c r="B184" t="n">
         <v>79084</v>
@@ -19721,13 +19725,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>494385</v>
+        <v>494243</v>
       </c>
       <c r="R184" t="n">
-        <v>6834229</v>
+        <v>6834445</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19782,13 +19786,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522151</t>
+          <t>https://artportalen.se/Sighting/129520975</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129522341</v>
+        <v>129522151</v>
       </c>
       <c r="B185" t="n">
         <v>79084</v>
@@ -19823,10 +19827,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>494345</v>
+        <v>494385</v>
       </c>
       <c r="R185" t="n">
-        <v>6834202</v>
+        <v>6834229</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19884,16 +19888,16 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522341</t>
+          <t>https://artportalen.se/Sighting/129522151</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>137094222</v>
+        <v>129522341</v>
       </c>
       <c r="B186" t="n">
-        <v>79292</v>
+        <v>79084</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19921,17 +19925,17 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>494690</v>
+        <v>494345</v>
       </c>
       <c r="R186" t="n">
-        <v>6834189</v>
+        <v>6834202</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19955,12 +19959,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -19986,16 +19990,16 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094222</t>
+          <t>https://artportalen.se/Sighting/129522341</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>137094663</v>
+        <v>137094222</v>
       </c>
       <c r="B187" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20027,13 +20031,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>494623</v>
+        <v>494690</v>
       </c>
       <c r="R187" t="n">
-        <v>6834359</v>
+        <v>6834189</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20077,27 +20081,27 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094663</t>
+          <t>https://artportalen.se/Sighting/137094222</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>137093799</v>
+        <v>137094663</v>
       </c>
       <c r="B188" t="n">
-        <v>80154</v>
+        <v>79296</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20105,21 +20109,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20129,10 +20133,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>494810</v>
+        <v>494623</v>
       </c>
       <c r="R188" t="n">
-        <v>6834174</v>
+        <v>6834359</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -20190,16 +20194,16 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137093799</t>
+          <t>https://artportalen.se/Sighting/137094663</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>137094121</v>
+        <v>137093799</v>
       </c>
       <c r="B189" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20231,10 +20235,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>494745</v>
+        <v>494810</v>
       </c>
       <c r="R189" t="n">
-        <v>6834204</v>
+        <v>6834174</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -20292,16 +20296,16 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137094121</t>
+          <t>https://artportalen.se/Sighting/137093799</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>137097767</v>
+        <v>137094121</v>
       </c>
       <c r="B190" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20329,14 +20333,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>494522</v>
+        <v>494745</v>
       </c>
       <c r="R190" t="n">
-        <v>6834661</v>
+        <v>6834204</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20394,16 +20398,16 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137097767</t>
+          <t>https://artportalen.se/Sighting/137094121</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>137098648</v>
+        <v>137097767</v>
       </c>
       <c r="B191" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20431,14 +20435,14 @@
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>494601</v>
+        <v>494522</v>
       </c>
       <c r="R191" t="n">
-        <v>6834481</v>
+        <v>6834661</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -20496,16 +20500,16 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137098648</t>
+          <t>https://artportalen.se/Sighting/137097767</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121313133</v>
+        <v>137098648</v>
       </c>
       <c r="B192" t="n">
-        <v>80432</v>
+        <v>80158</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20513,37 +20517,37 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>493849</v>
+        <v>494601</v>
       </c>
       <c r="R192" t="n">
-        <v>6834871</v>
+        <v>6834481</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20567,17 +20571,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>På rönn</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20592,24 +20591,24 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313133</t>
+          <t>https://artportalen.se/Sighting/137098648</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121313322</v>
+        <v>121313133</v>
       </c>
       <c r="B193" t="n">
         <v>80432</v>
@@ -20644,13 +20643,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>493813</v>
+        <v>493849</v>
       </c>
       <c r="R193" t="n">
-        <v>6834953</v>
+        <v>6834871</v>
       </c>
       <c r="S193" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20680,6 +20679,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20694,24 +20698,24 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313322</t>
+          <t>https://artportalen.se/Sighting/121313133</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129512470</v>
+        <v>121313322</v>
       </c>
       <c r="B194" t="n">
         <v>80432</v>
@@ -20742,17 +20746,17 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>494652</v>
+        <v>493813</v>
       </c>
       <c r="R194" t="n">
-        <v>6833984</v>
+        <v>6834953</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20776,12 +20780,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20807,13 +20811,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512470</t>
+          <t>https://artportalen.se/Sighting/121313322</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129512549</v>
+        <v>129512470</v>
       </c>
       <c r="B195" t="n">
         <v>80432</v>
@@ -20848,10 +20852,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>494625</v>
+        <v>494652</v>
       </c>
       <c r="R195" t="n">
-        <v>6834032</v>
+        <v>6833984</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20909,13 +20913,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512549</t>
+          <t>https://artportalen.se/Sighting/129512470</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129521092</v>
+        <v>129512549</v>
       </c>
       <c r="B196" t="n">
         <v>80432</v>
@@ -20950,10 +20954,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>494222</v>
+        <v>494625</v>
       </c>
       <c r="R196" t="n">
-        <v>6834398</v>
+        <v>6834032</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20980,12 +20984,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21011,13 +21015,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521092</t>
+          <t>https://artportalen.se/Sighting/129512549</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129521874</v>
+        <v>129521092</v>
       </c>
       <c r="B197" t="n">
         <v>80432</v>
@@ -21048,14 +21052,14 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>494355</v>
+        <v>494222</v>
       </c>
       <c r="R197" t="n">
-        <v>6834295</v>
+        <v>6834398</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21102,24 +21106,24 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521874</t>
+          <t>https://artportalen.se/Sighting/129521092</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129521977</v>
+        <v>129521874</v>
       </c>
       <c r="B198" t="n">
         <v>80432</v>
@@ -21150,14 +21154,14 @@
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>494334</v>
+        <v>494355</v>
       </c>
       <c r="R198" t="n">
-        <v>6834144</v>
+        <v>6834295</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21204,24 +21208,24 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521977</t>
+          <t>https://artportalen.se/Sighting/129521874</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129522012</v>
+        <v>129521977</v>
       </c>
       <c r="B199" t="n">
         <v>80432</v>
@@ -21256,10 +21260,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>494337</v>
+        <v>494334</v>
       </c>
       <c r="R199" t="n">
-        <v>6834146</v>
+        <v>6834144</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21317,13 +21321,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522012</t>
+          <t>https://artportalen.se/Sighting/129521977</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129522173</v>
+        <v>129522012</v>
       </c>
       <c r="B200" t="n">
         <v>80432</v>
@@ -21358,10 +21362,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>494418</v>
+        <v>494337</v>
       </c>
       <c r="R200" t="n">
-        <v>6834113</v>
+        <v>6834146</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21419,13 +21423,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522173</t>
+          <t>https://artportalen.se/Sighting/129522012</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129524119</v>
+        <v>129522173</v>
       </c>
       <c r="B201" t="n">
         <v>80432</v>
@@ -21460,10 +21464,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>494556</v>
+        <v>494418</v>
       </c>
       <c r="R201" t="n">
-        <v>6834468</v>
+        <v>6834113</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21521,13 +21525,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524119</t>
+          <t>https://artportalen.se/Sighting/129522173</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129524581</v>
+        <v>129524119</v>
       </c>
       <c r="B202" t="n">
         <v>80432</v>
@@ -21558,14 +21562,14 @@
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>494323</v>
+        <v>494556</v>
       </c>
       <c r="R202" t="n">
-        <v>6834627</v>
+        <v>6834468</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21612,24 +21616,24 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524581</t>
+          <t>https://artportalen.se/Sighting/129524119</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129524595</v>
+        <v>129524581</v>
       </c>
       <c r="B203" t="n">
         <v>80432</v>
@@ -21664,10 +21668,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>494349</v>
+        <v>494323</v>
       </c>
       <c r="R203" t="n">
-        <v>6834611</v>
+        <v>6834627</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21725,13 +21729,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524595</t>
+          <t>https://artportalen.se/Sighting/129524581</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129524606</v>
+        <v>129524595</v>
       </c>
       <c r="B204" t="n">
         <v>80432</v>
@@ -21766,10 +21770,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>494333</v>
+        <v>494349</v>
       </c>
       <c r="R204" t="n">
-        <v>6834609</v>
+        <v>6834611</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21827,13 +21831,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524606</t>
+          <t>https://artportalen.se/Sighting/129524595</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129524680</v>
+        <v>129524606</v>
       </c>
       <c r="B205" t="n">
         <v>80432</v>
@@ -21868,10 +21872,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>494357</v>
+        <v>494333</v>
       </c>
       <c r="R205" t="n">
-        <v>6834592</v>
+        <v>6834609</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21929,16 +21933,16 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524680</t>
+          <t>https://artportalen.se/Sighting/129524606</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>137095442</v>
+        <v>129524680</v>
       </c>
       <c r="B206" t="n">
-        <v>80650</v>
+        <v>80432</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21966,17 +21970,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>494597</v>
+        <v>494357</v>
       </c>
       <c r="R206" t="n">
-        <v>6834225</v>
+        <v>6834592</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22000,12 +22004,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22020,27 +22024,27 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095442</t>
+          <t>https://artportalen.se/Sighting/129524680</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>137098828</v>
+        <v>137095442</v>
       </c>
       <c r="B207" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22072,10 +22076,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>494651</v>
+        <v>494597</v>
       </c>
       <c r="R207" t="n">
-        <v>6834480</v>
+        <v>6834225</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -22133,54 +22137,54 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137098828</t>
+          <t>https://artportalen.se/Sighting/137095442</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121313317</v>
+        <v>137098828</v>
       </c>
       <c r="B208" t="n">
-        <v>80461</v>
+        <v>80654</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>493813</v>
+        <v>494651</v>
       </c>
       <c r="R208" t="n">
-        <v>6834953</v>
+        <v>6834480</v>
       </c>
       <c r="S208" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22204,12 +22208,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22235,13 +22239,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121313317</t>
+          <t>https://artportalen.se/Sighting/137098828</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129521887</v>
+        <v>121313317</v>
       </c>
       <c r="B209" t="n">
         <v>80461</v>
@@ -22272,17 +22276,17 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>494350</v>
+        <v>493813</v>
       </c>
       <c r="R209" t="n">
-        <v>6834298</v>
+        <v>6834953</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22306,12 +22310,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22326,27 +22330,27 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521887</t>
+          <t>https://artportalen.se/Sighting/121313317</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129512556</v>
+        <v>129521887</v>
       </c>
       <c r="B210" t="n">
-        <v>80468</v>
+        <v>80461</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22354,34 +22358,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>494625</v>
+        <v>494350</v>
       </c>
       <c r="R210" t="n">
-        <v>6834033</v>
+        <v>6834298</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22408,12 +22412,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -22428,62 +22432,62 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129512556</t>
+          <t>https://artportalen.se/Sighting/129521887</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129523028</v>
+        <v>129512556</v>
       </c>
       <c r="B211" t="n">
-        <v>78334</v>
+        <v>80468</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R211" t="n">
-        <v>6834263</v>
+        <v>6834033</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22510,12 +22514,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22530,70 +22534,62 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523028</t>
+          <t>https://artportalen.se/Sighting/129512556</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>134851532</v>
+        <v>129523028</v>
       </c>
       <c r="B212" t="n">
-        <v>58005</v>
+        <v>78334</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>494480</v>
+        <v>494500</v>
       </c>
       <c r="R212" t="n">
-        <v>6834438</v>
+        <v>6834263</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22620,12 +22616,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22640,44 +22636,44 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134851532</t>
+          <t>https://artportalen.se/Sighting/129523028</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>137097713</v>
+        <v>134851532</v>
       </c>
       <c r="B213" t="n">
-        <v>58035</v>
+        <v>58005</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -22686,19 +22682,27 @@
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>494452</v>
+        <v>494480</v>
       </c>
       <c r="R213" t="n">
-        <v>6834642</v>
+        <v>6834438</v>
       </c>
       <c r="S213" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -22722,17 +22726,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22747,44 +22746,44 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137097713</t>
+          <t>https://artportalen.se/Sighting/134851532</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129522100</v>
+        <v>137097713</v>
       </c>
       <c r="B214" t="n">
-        <v>58327</v>
+        <v>58038</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -22795,17 +22794,17 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>494368</v>
+        <v>494452</v>
       </c>
       <c r="R214" t="n">
-        <v>6834126</v>
+        <v>6834642</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -22829,12 +22828,17 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -22860,38 +22864,38 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522100</t>
+          <t>https://artportalen.se/Sighting/137097713</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129522021</v>
+        <v>129522100</v>
       </c>
       <c r="B215" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22901,10 +22905,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>494337</v>
+        <v>494368</v>
       </c>
       <c r="R215" t="n">
-        <v>6834149</v>
+        <v>6834126</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -22962,13 +22966,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522021</t>
+          <t>https://artportalen.se/Sighting/129522100</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129523899</v>
+        <v>129522021</v>
       </c>
       <c r="B216" t="n">
         <v>58114</v>
@@ -23003,10 +23007,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>494543</v>
+        <v>494337</v>
       </c>
       <c r="R216" t="n">
-        <v>6834251</v>
+        <v>6834149</v>
       </c>
       <c r="S216" t="n">
         <v>15</v>
@@ -23064,16 +23068,16 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523899</t>
+          <t>https://artportalen.se/Sighting/129522021</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>137095389</v>
+        <v>129523899</v>
       </c>
       <c r="B217" t="n">
-        <v>58196</v>
+        <v>58114</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23101,17 +23105,17 @@
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>494614</v>
+        <v>494543</v>
       </c>
       <c r="R217" t="n">
-        <v>6834224</v>
+        <v>6834251</v>
       </c>
       <c r="S217" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23135,12 +23139,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23166,54 +23170,54 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095389</t>
+          <t>https://artportalen.se/Sighting/129523899</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121314344</v>
+        <v>137095389</v>
       </c>
       <c r="B218" t="n">
-        <v>99118</v>
+        <v>58199</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>493875</v>
+        <v>494614</v>
       </c>
       <c r="R218" t="n">
-        <v>6834814</v>
+        <v>6834224</v>
       </c>
       <c r="S218" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23237,12 +23241,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23257,24 +23261,24 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121314344</t>
+          <t>https://artportalen.se/Sighting/137095389</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121314972</v>
+        <v>121314344</v>
       </c>
       <c r="B219" t="n">
         <v>99118</v>
@@ -23309,10 +23313,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>493938</v>
+        <v>493875</v>
       </c>
       <c r="R219" t="n">
-        <v>6834637</v>
+        <v>6834814</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -23370,13 +23374,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121314972</t>
+          <t>https://artportalen.se/Sighting/121314344</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121315050</v>
+        <v>121314972</v>
       </c>
       <c r="B220" t="n">
         <v>99118</v>
@@ -23411,10 +23415,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>493937</v>
+        <v>493938</v>
       </c>
       <c r="R220" t="n">
-        <v>6834639</v>
+        <v>6834637</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -23472,13 +23476,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315050</t>
+          <t>https://artportalen.se/Sighting/121314972</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121315126</v>
+        <v>121315050</v>
       </c>
       <c r="B221" t="n">
         <v>99118</v>
@@ -23513,13 +23517,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>493940</v>
+        <v>493937</v>
       </c>
       <c r="R221" t="n">
-        <v>6834631</v>
+        <v>6834639</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -23549,11 +23553,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23579,13 +23578,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315126</t>
+          <t>https://artportalen.se/Sighting/121315050</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121315885</v>
+        <v>121315126</v>
       </c>
       <c r="B222" t="n">
         <v>99118</v>
@@ -23620,13 +23619,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>493917</v>
+        <v>493940</v>
       </c>
       <c r="R222" t="n">
-        <v>6834746</v>
+        <v>6834631</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -23656,6 +23655,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23681,13 +23685,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121315885</t>
+          <t>https://artportalen.se/Sighting/121315126</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121316014</v>
+        <v>121315885</v>
       </c>
       <c r="B223" t="n">
         <v>99118</v>
@@ -23722,10 +23726,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>493896</v>
+        <v>493917</v>
       </c>
       <c r="R223" t="n">
-        <v>6834747</v>
+        <v>6834746</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -23783,13 +23787,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316014</t>
+          <t>https://artportalen.se/Sighting/121315885</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121316066</v>
+        <v>121316014</v>
       </c>
       <c r="B224" t="n">
         <v>99118</v>
@@ -23827,7 +23831,7 @@
         <v>493896</v>
       </c>
       <c r="R224" t="n">
-        <v>6834749</v>
+        <v>6834747</v>
       </c>
       <c r="S224" t="n">
         <v>15</v>
@@ -23885,13 +23889,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316066</t>
+          <t>https://artportalen.se/Sighting/121316014</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121316126</v>
+        <v>121316066</v>
       </c>
       <c r="B225" t="n">
         <v>99118</v>
@@ -23926,10 +23930,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>493898</v>
+        <v>493896</v>
       </c>
       <c r="R225" t="n">
-        <v>6834798</v>
+        <v>6834749</v>
       </c>
       <c r="S225" t="n">
         <v>15</v>
@@ -23987,13 +23991,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316126</t>
+          <t>https://artportalen.se/Sighting/121316066</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121316297</v>
+        <v>121316126</v>
       </c>
       <c r="B226" t="n">
         <v>99118</v>
@@ -24028,13 +24032,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>493886</v>
+        <v>493898</v>
       </c>
       <c r="R226" t="n">
-        <v>6834817</v>
+        <v>6834798</v>
       </c>
       <c r="S226" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -24089,13 +24093,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316297</t>
+          <t>https://artportalen.se/Sighting/121316126</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121316463</v>
+        <v>121316297</v>
       </c>
       <c r="B227" t="n">
         <v>99118</v>
@@ -24130,13 +24134,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>493838</v>
+        <v>493886</v>
       </c>
       <c r="R227" t="n">
-        <v>6834855</v>
+        <v>6834817</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -24191,13 +24195,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121316463</t>
+          <t>https://artportalen.se/Sighting/121316297</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121462959</v>
+        <v>121316463</v>
       </c>
       <c r="B228" t="n">
         <v>99118</v>
@@ -24225,29 +24229,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>494001</v>
+        <v>493838</v>
       </c>
       <c r="R228" t="n">
-        <v>6834589</v>
+        <v>6834855</v>
       </c>
       <c r="S228" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -24271,22 +24266,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24301,24 +24286,24 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121462959</t>
+          <t>https://artportalen.se/Sighting/121316463</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121463131</v>
+        <v>121462959</v>
       </c>
       <c r="B229" t="n">
         <v>99118</v>
@@ -24348,30 +24333,27 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>494081</v>
+        <v>494001</v>
       </c>
       <c r="R229" t="n">
-        <v>6834614</v>
+        <v>6834589</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -24400,7 +24382,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -24410,7 +24392,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24419,31 +24401,30 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
+          <t>Bo karlstens, Göran Ehn, Lars-Erik Nilsson, Lisa Olson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463131</t>
+          <t>https://artportalen.se/Sighting/121462959</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121463365</v>
+        <v>121463131</v>
       </c>
       <c r="B230" t="n">
         <v>99118</v>
@@ -24473,7 +24454,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -24490,10 +24471,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>494086</v>
+        <v>494081</v>
       </c>
       <c r="R230" t="n">
-        <v>6834603</v>
+        <v>6834614</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24525,7 +24506,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -24535,7 +24516,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24562,13 +24543,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463365</t>
+          <t>https://artportalen.se/Sighting/121463131</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121463743</v>
+        <v>121463365</v>
       </c>
       <c r="B231" t="n">
         <v>99118</v>
@@ -24598,7 +24579,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -24615,10 +24596,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>494116</v>
+        <v>494086</v>
       </c>
       <c r="R231" t="n">
-        <v>6834573</v>
+        <v>6834603</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24650,7 +24631,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -24660,7 +24641,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24687,13 +24668,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121463743</t>
+          <t>https://artportalen.se/Sighting/121463365</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129456055</v>
+        <v>121463743</v>
       </c>
       <c r="B232" t="n">
         <v>99118</v>
@@ -24723,24 +24704,27 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>493817</v>
+        <v>494116</v>
       </c>
       <c r="R232" t="n">
-        <v>6834930</v>
+        <v>6834573</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24767,12 +24751,22 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24781,30 +24775,31 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn, Lisa Olson, Bo karlstens, Lars-Erik Nilsson, Philipp Weiss, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456055</t>
+          <t>https://artportalen.se/Sighting/121463743</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129456103</v>
+        <v>129456055</v>
       </c>
       <c r="B233" t="n">
         <v>99118</v>
@@ -24834,7 +24829,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -24851,7 +24846,7 @@
         <v>493817</v>
       </c>
       <c r="R233" t="n">
-        <v>6834939</v>
+        <v>6834930</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24909,13 +24904,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456103</t>
+          <t>https://artportalen.se/Sighting/129456055</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129456176</v>
+        <v>129456103</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -24945,7 +24940,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -24959,10 +24954,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>493813</v>
+        <v>493817</v>
       </c>
       <c r="R234" t="n">
-        <v>6834955</v>
+        <v>6834939</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25020,13 +25015,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456176</t>
+          <t>https://artportalen.se/Sighting/129456103</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129456885</v>
+        <v>129456176</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -25056,7 +25051,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -25070,10 +25065,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>493815</v>
+        <v>493813</v>
       </c>
       <c r="R235" t="n">
-        <v>6834917</v>
+        <v>6834955</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25131,13 +25126,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129456885</t>
+          <t>https://artportalen.se/Sighting/129456176</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129514113</v>
+        <v>129456885</v>
       </c>
       <c r="B236" t="n">
         <v>99118</v>
@@ -25165,17 +25160,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>494256</v>
+        <v>493815</v>
       </c>
       <c r="R236" t="n">
-        <v>6834732</v>
+        <v>6834917</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25202,12 +25206,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25233,13 +25237,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129514113</t>
+          <t>https://artportalen.se/Sighting/129456885</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129520989</v>
+        <v>129514113</v>
       </c>
       <c r="B237" t="n">
         <v>99118</v>
@@ -25267,26 +25271,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>494262</v>
+        <v>494256</v>
       </c>
       <c r="R237" t="n">
-        <v>6834427</v>
+        <v>6834732</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25313,12 +25308,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25344,13 +25339,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129520989</t>
+          <t>https://artportalen.se/Sighting/129514113</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129521085</v>
+        <v>129520989</v>
       </c>
       <c r="B238" t="n">
         <v>99118</v>
@@ -25378,17 +25373,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>494228</v>
+        <v>494262</v>
       </c>
       <c r="R238" t="n">
-        <v>6834405</v>
+        <v>6834427</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25446,13 +25450,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521085</t>
+          <t>https://artportalen.se/Sighting/129520989</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129521897</v>
+        <v>129521085</v>
       </c>
       <c r="B239" t="n">
         <v>99118</v>
@@ -25487,10 +25491,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>494323</v>
+        <v>494228</v>
       </c>
       <c r="R239" t="n">
-        <v>6834131</v>
+        <v>6834405</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25548,13 +25552,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521897</t>
+          <t>https://artportalen.se/Sighting/129521085</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129522294</v>
+        <v>129521897</v>
       </c>
       <c r="B240" t="n">
         <v>99118</v>
@@ -25589,10 +25593,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>494419</v>
+        <v>494323</v>
       </c>
       <c r="R240" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25650,13 +25654,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522294</t>
+          <t>https://artportalen.se/Sighting/129521897</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129522417</v>
+        <v>129522294</v>
       </c>
       <c r="B241" t="n">
         <v>99118</v>
@@ -25691,10 +25695,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>494442</v>
+        <v>494419</v>
       </c>
       <c r="R241" t="n">
-        <v>6834141</v>
+        <v>6834113</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25752,13 +25756,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522417</t>
+          <t>https://artportalen.se/Sighting/129522294</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129522632</v>
+        <v>129522417</v>
       </c>
       <c r="B242" t="n">
         <v>99118</v>
@@ -25786,26 +25790,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>494455</v>
+        <v>494442</v>
       </c>
       <c r="R242" t="n">
-        <v>6834185</v>
+        <v>6834141</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25863,13 +25858,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522632</t>
+          <t>https://artportalen.se/Sighting/129522417</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129522644</v>
+        <v>129522632</v>
       </c>
       <c r="B243" t="n">
         <v>99118</v>
@@ -25913,10 +25908,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>494450</v>
+        <v>494455</v>
       </c>
       <c r="R243" t="n">
-        <v>6834178</v>
+        <v>6834185</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25974,13 +25969,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522644</t>
+          <t>https://artportalen.se/Sighting/129522632</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129524059</v>
+        <v>129522644</v>
       </c>
       <c r="B244" t="n">
         <v>99118</v>
@@ -26010,7 +26005,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -26020,14 +26015,14 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>494582</v>
+        <v>494450</v>
       </c>
       <c r="R244" t="n">
-        <v>6834361</v>
+        <v>6834178</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26074,24 +26069,24 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524059</t>
+          <t>https://artportalen.se/Sighting/129522644</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129524619</v>
+        <v>129524059</v>
       </c>
       <c r="B245" t="n">
         <v>99118</v>
@@ -26121,7 +26116,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -26135,10 +26130,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>494338</v>
+        <v>494582</v>
       </c>
       <c r="R245" t="n">
-        <v>6834601</v>
+        <v>6834361</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26196,13 +26191,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129524619</t>
+          <t>https://artportalen.se/Sighting/129524059</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129525359</v>
+        <v>129524619</v>
       </c>
       <c r="B246" t="n">
         <v>99118</v>
@@ -26232,7 +26227,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -26246,10 +26241,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>493934</v>
+        <v>494338</v>
       </c>
       <c r="R246" t="n">
-        <v>6834670</v>
+        <v>6834601</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26307,13 +26302,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129525359</t>
+          <t>https://artportalen.se/Sighting/129524619</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>129525370</v>
+        <v>129525359</v>
       </c>
       <c r="B247" t="n">
         <v>99118</v>
@@ -26341,17 +26336,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P247" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>493942</v>
+        <v>493934</v>
       </c>
       <c r="R247" t="n">
-        <v>6834657</v>
+        <v>6834670</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26409,54 +26413,54 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129525370</t>
+          <t>https://artportalen.se/Sighting/129525359</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121464008</v>
+        <v>129525370</v>
       </c>
       <c r="B248" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>494068</v>
+        <v>493942</v>
       </c>
       <c r="R248" t="n">
-        <v>6834592</v>
+        <v>6834657</v>
       </c>
       <c r="S248" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26480,22 +26484,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26510,24 +26504,24 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121464008</t>
+          <t>https://artportalen.se/Sighting/129525370</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129511943</v>
+        <v>121464008</v>
       </c>
       <c r="B249" t="n">
         <v>79085</v>
@@ -26562,13 +26556,13 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>494635</v>
+        <v>494068</v>
       </c>
       <c r="R249" t="n">
-        <v>6834347</v>
+        <v>6834592</v>
       </c>
       <c r="S249" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26592,12 +26586,22 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26612,24 +26616,24 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129511943</t>
+          <t>https://artportalen.se/Sighting/121464008</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129521425</v>
+        <v>129511943</v>
       </c>
       <c r="B250" t="n">
         <v>79085</v>
@@ -26660,14 +26664,14 @@
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>494187</v>
+        <v>494635</v>
       </c>
       <c r="R250" t="n">
-        <v>6834373</v>
+        <v>6834347</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26694,12 +26698,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26714,24 +26718,24 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521425</t>
+          <t>https://artportalen.se/Sighting/129511943</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129521475</v>
+        <v>129521425</v>
       </c>
       <c r="B251" t="n">
         <v>79085</v>
@@ -26762,14 +26766,14 @@
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>494181</v>
+        <v>494187</v>
       </c>
       <c r="R251" t="n">
-        <v>6834367</v>
+        <v>6834373</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26816,24 +26820,24 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521475</t>
+          <t>https://artportalen.se/Sighting/129521425</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129521663</v>
+        <v>129521475</v>
       </c>
       <c r="B252" t="n">
         <v>79085</v>
@@ -26864,14 +26868,14 @@
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>494242</v>
+        <v>494181</v>
       </c>
       <c r="R252" t="n">
-        <v>6834295</v>
+        <v>6834367</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26918,24 +26922,24 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129521663</t>
+          <t>https://artportalen.se/Sighting/129521475</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129522147</v>
+        <v>129521663</v>
       </c>
       <c r="B253" t="n">
         <v>79085</v>
@@ -26970,10 +26974,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>494385</v>
+        <v>494242</v>
       </c>
       <c r="R253" t="n">
-        <v>6834229</v>
+        <v>6834295</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27031,13 +27035,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522147</t>
+          <t>https://artportalen.se/Sighting/129521663</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>129522256</v>
+        <v>129522147</v>
       </c>
       <c r="B254" t="n">
         <v>79085</v>
@@ -27072,10 +27076,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>494384</v>
+        <v>494385</v>
       </c>
       <c r="R254" t="n">
-        <v>6834211</v>
+        <v>6834229</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27133,13 +27137,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522256</t>
+          <t>https://artportalen.se/Sighting/129522147</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>129522517</v>
+        <v>129522256</v>
       </c>
       <c r="B255" t="n">
         <v>79085</v>
@@ -27170,14 +27174,14 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>494455</v>
+        <v>494384</v>
       </c>
       <c r="R255" t="n">
-        <v>6834176</v>
+        <v>6834211</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27224,24 +27228,24 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522517</t>
+          <t>https://artportalen.se/Sighting/129522256</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>129523234</v>
+        <v>129522517</v>
       </c>
       <c r="B256" t="n">
         <v>79085</v>
@@ -27272,14 +27276,14 @@
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>494472</v>
+        <v>494455</v>
       </c>
       <c r="R256" t="n">
-        <v>6834268</v>
+        <v>6834176</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27326,27 +27330,27 @@
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129523234</t>
+          <t>https://artportalen.se/Sighting/129522517</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>137097763</v>
+        <v>129523234</v>
       </c>
       <c r="B257" t="n">
-        <v>79293</v>
+        <v>79085</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -27374,17 +27378,17 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>494522</v>
+        <v>494472</v>
       </c>
       <c r="R257" t="n">
-        <v>6834661</v>
+        <v>6834268</v>
       </c>
       <c r="S257" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27408,12 +27412,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27428,27 +27432,27 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137097763</t>
+          <t>https://artportalen.se/Sighting/129523234</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>137098795</v>
+        <v>137097763</v>
       </c>
       <c r="B258" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27476,14 +27480,14 @@
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>494632</v>
+        <v>494522</v>
       </c>
       <c r="R258" t="n">
-        <v>6834484</v>
+        <v>6834661</v>
       </c>
       <c r="S258" t="n">
         <v>5</v>
@@ -27541,16 +27545,16 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137098795</t>
+          <t>https://artportalen.se/Sighting/137097763</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>129522138</v>
+        <v>137098795</v>
       </c>
       <c r="B259" t="n">
-        <v>79917</v>
+        <v>79297</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -27558,37 +27562,37 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>494375</v>
+        <v>494632</v>
       </c>
       <c r="R259" t="n">
-        <v>6834215</v>
+        <v>6834484</v>
       </c>
       <c r="S259" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -27612,12 +27616,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27632,68 +27636,65 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129522138</t>
+          <t>https://artportalen.se/Sighting/137098795</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>136488052</v>
+        <v>129522138</v>
       </c>
       <c r="B260" t="n">
-        <v>90955</v>
+        <v>79917</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>245044</v>
+        <v>229821</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>494214</v>
+        <v>494375</v>
       </c>
       <c r="R260" t="n">
-        <v>6834723</v>
+        <v>6834215</v>
       </c>
       <c r="S260" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -27717,75 +27718,69 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Sex fruktkroppar i sandblotta invid myr.</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD260" t="b">
         <v>0</v>
       </c>
       <c r="AE260" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF260" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136488052</t>
+          <t>https://artportalen.se/Sighting/129522138</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>136487945</v>
+        <v>136488052</v>
       </c>
       <c r="B261" t="n">
-        <v>93454</v>
+        <v>90959</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>6332770</v>
+        <v>245044</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>A.Riva</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27798,7 +27793,7 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>494213</v>
+        <v>494214</v>
       </c>
       <c r="R261" t="n">
         <v>6834723</v>
@@ -27836,11 +27831,16 @@
           <t>2026-09-09</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Sex fruktkroppar i sandblotta invid myr.</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
@@ -27859,6 +27859,112 @@
       </c>
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136488052</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>136487945</v>
+      </c>
+      <c r="B262" t="n">
+        <v>93454</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Korplamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>494213</v>
+      </c>
+      <c r="R262" t="n">
+        <v>6834723</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136487945</t>
         </is>
@@ -28126,6 +28232,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
